--- a/data_folder/carcomposition_mockup/input_data/case.xlsx
+++ b/data_folder/carcomposition_mockup/input_data/case.xlsx
@@ -10,6 +10,7 @@
     <sheet name="source" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="processes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TCs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="_lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,8 +419,8 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,7 @@
           <t>material_suffix</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -519,6 +521,7 @@
           <t>groups</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -533,6 +536,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -977,7 +985,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1038,7 +1045,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1089,8 +1095,6 @@
       <c r="G4" t="n">
         <v>0.82</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>1</t>
@@ -1156,7 +1160,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1217,7 +1220,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1268,8 +1270,6 @@
       <c r="G7" t="n">
         <v>0.02</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1335,7 +1335,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1396,7 +1395,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1447,8 +1445,6 @@
       <c r="G10" t="n">
         <v>0.82</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1514,7 +1510,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1575,7 +1570,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1626,8 +1620,6 @@
       <c r="G13" t="n">
         <v>0.82</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1693,7 +1685,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1754,7 +1745,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1805,8 +1795,6 @@
       <c r="G16" t="n">
         <v>0.82</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1872,7 +1860,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1933,7 +1920,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1984,8 +1970,6 @@
       <c r="G19" t="n">
         <v>0.52</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>1</t>
@@ -2051,7 +2035,6 @@
           <t>0.894444</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2112,7 +2095,6 @@
           <t>0.105556</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2163,8 +2145,6 @@
       <c r="G22" t="n">
         <v>0.17</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>1</t>
@@ -2230,7 +2210,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2291,7 +2270,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2342,8 +2320,6 @@
       <c r="G25" t="n">
         <v>0.82</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>1</t>
@@ -2409,7 +2385,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2470,7 +2445,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2521,8 +2495,6 @@
       <c r="G28" t="n">
         <v>0.82</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>1</t>
@@ -2588,7 +2560,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2649,7 +2620,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2700,8 +2670,6 @@
       <c r="G31" t="n">
         <v>0.27</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>1</t>
@@ -2767,7 +2735,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2828,7 +2795,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2879,8 +2845,6 @@
       <c r="G34" t="n">
         <v>0.82</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>1</t>
@@ -2946,7 +2910,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3007,7 +2970,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3058,8 +3020,6 @@
       <c r="G37" t="n">
         <v>0.37</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>1</t>
@@ -3125,7 +3085,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3186,7 +3145,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3237,8 +3195,6 @@
       <c r="G40" t="n">
         <v>0.82</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>1</t>
@@ -3304,7 +3260,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3365,7 +3320,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3416,8 +3370,6 @@
       <c r="G43" t="n">
         <v>0.82</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>1</t>
@@ -3483,7 +3435,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3544,7 +3495,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3595,8 +3545,6 @@
       <c r="G46" t="n">
         <v>0.02</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>1</t>
@@ -3662,7 +3610,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3723,7 +3670,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3774,8 +3720,6 @@
       <c r="G49" t="n">
         <v>0.82</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>1</t>
@@ -3841,7 +3785,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3902,7 +3845,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3953,8 +3895,6 @@
       <c r="G52" t="n">
         <v>0.82</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>1</t>
@@ -4020,7 +3960,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4081,7 +4020,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4132,8 +4070,6 @@
       <c r="G55" t="n">
         <v>0.52</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>1</t>
@@ -4199,7 +4135,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4260,7 +4195,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4311,8 +4245,6 @@
       <c r="G58" t="n">
         <v>0.82</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>1</t>
@@ -4378,7 +4310,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4439,7 +4370,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4490,8 +4420,6 @@
       <c r="G61" t="n">
         <v>0.82</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>1</t>
@@ -4557,7 +4485,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4618,7 +4545,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4669,8 +4595,6 @@
       <c r="G64" t="n">
         <v>0.82</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>1</t>
@@ -4736,7 +4660,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4797,7 +4720,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4848,8 +4770,6 @@
       <c r="G67" t="n">
         <v>0.82</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>1</t>
@@ -4915,7 +4835,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4976,7 +4895,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5027,8 +4945,6 @@
       <c r="G70" t="n">
         <v>0.37</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>1</t>
@@ -5094,7 +5010,6 @@
           <t>0.894444</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5155,7 +5070,6 @@
           <t>0.105556</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5206,8 +5120,6 @@
       <c r="G73" t="n">
         <v>0.17</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>1</t>
@@ -5273,7 +5185,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5334,7 +5245,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5385,8 +5295,6 @@
       <c r="G76" t="n">
         <v>0.82</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>1</t>
@@ -5452,7 +5360,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5513,7 +5420,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5564,8 +5470,6 @@
       <c r="G79" t="n">
         <v>0.82</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>1</t>
@@ -5631,7 +5535,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5692,7 +5595,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5743,8 +5645,6 @@
       <c r="G82" t="n">
         <v>0.27</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>1</t>
@@ -5810,7 +5710,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5871,7 +5770,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5922,8 +5820,6 @@
       <c r="G85" t="n">
         <v>0.82</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>1</t>
@@ -5989,7 +5885,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6050,7 +5945,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6101,8 +5995,6 @@
       <c r="G88" t="n">
         <v>0.37</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>1</t>
@@ -6168,7 +6060,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6229,7 +6120,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6280,8 +6170,6 @@
       <c r="G91" t="n">
         <v>0.82</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>1</t>
@@ -6347,7 +6235,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6408,7 +6295,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6459,8 +6345,6 @@
       <c r="G94" t="n">
         <v>0.02</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>1</t>
@@ -6526,7 +6410,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6587,7 +6470,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6638,8 +6520,6 @@
       <c r="G97" t="n">
         <v>0.82</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>1</t>
@@ -6705,7 +6585,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6766,7 +6645,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6817,8 +6695,6 @@
       <c r="G100" t="n">
         <v>0.02</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>1</t>
@@ -6884,7 +6760,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6945,7 +6820,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6996,8 +6870,6 @@
       <c r="G103" t="n">
         <v>0.82</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>1</t>
@@ -7063,7 +6935,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7124,7 +6995,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7175,8 +7045,6 @@
       <c r="G106" t="n">
         <v>0.82</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>1</t>
@@ -7242,7 +7110,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7303,7 +7170,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7354,8 +7220,6 @@
       <c r="G109" t="n">
         <v>0.52</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>1</t>
@@ -7421,7 +7285,6 @@
           <t>0.894444</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7482,7 +7345,6 @@
           <t>0.105556</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7533,8 +7395,6 @@
       <c r="G112" t="n">
         <v>0.17</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>1</t>
@@ -7600,7 +7460,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7661,7 +7520,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7712,8 +7570,6 @@
       <c r="G115" t="n">
         <v>0.82</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>1</t>
@@ -7779,7 +7635,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7840,7 +7695,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7891,8 +7745,6 @@
       <c r="G118" t="n">
         <v>0.82</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>1</t>
@@ -7958,7 +7810,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8019,7 +7870,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8070,8 +7920,6 @@
       <c r="G121" t="n">
         <v>0.27</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>1</t>
@@ -8137,7 +7985,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8198,7 +8045,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8249,8 +8095,6 @@
       <c r="G124" t="n">
         <v>0.82</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>1</t>
@@ -8316,7 +8160,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8377,7 +8220,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8428,8 +8270,6 @@
       <c r="G127" t="n">
         <v>0.37</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>1</t>
@@ -8495,7 +8335,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8556,7 +8395,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8607,8 +8445,6 @@
       <c r="G130" t="n">
         <v>0.82</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>1</t>
@@ -8674,7 +8510,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8735,7 +8570,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8786,8 +8620,6 @@
       <c r="G133" t="n">
         <v>0.82</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>1</t>
@@ -8853,7 +8685,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8914,7 +8745,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8965,8 +8795,6 @@
       <c r="G136" t="n">
         <v>0.82</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>1</t>
@@ -9032,7 +8860,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9093,7 +8920,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9144,8 +8970,6 @@
       <c r="G139" t="n">
         <v>0.02</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>1</t>
@@ -9211,7 +9035,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9272,7 +9095,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9323,8 +9145,6 @@
       <c r="G142" t="n">
         <v>0.82</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>1</t>
@@ -9390,7 +9210,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9451,7 +9270,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9502,8 +9320,6 @@
       <c r="G145" t="n">
         <v>0.02</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>1</t>
@@ -9569,7 +9385,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9630,7 +9445,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9681,8 +9495,6 @@
       <c r="G148" t="n">
         <v>0.82</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>1</t>
@@ -9748,7 +9560,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9809,7 +9620,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9860,8 +9670,6 @@
       <c r="G151" t="n">
         <v>0.82</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>1</t>
@@ -9927,7 +9735,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9988,7 +9795,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10039,8 +9845,6 @@
       <c r="G154" t="n">
         <v>0.52</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>1</t>
@@ -10106,7 +9910,6 @@
           <t>0.894444</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10167,7 +9970,6 @@
           <t>0.105556</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10218,8 +10020,6 @@
       <c r="G157" t="n">
         <v>0.17</v>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>1</t>
@@ -10285,7 +10085,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10346,7 +10145,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10397,8 +10195,6 @@
       <c r="G160" t="n">
         <v>0.82</v>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>1</t>
@@ -10464,7 +10260,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10525,7 +10320,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10576,8 +10370,6 @@
       <c r="G163" t="n">
         <v>0.82</v>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>1</t>
@@ -10643,7 +10435,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10704,7 +10495,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10755,8 +10545,6 @@
       <c r="G166" t="n">
         <v>0.27</v>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>1</t>
@@ -10822,7 +10610,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10883,7 +10670,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10934,8 +10720,6 @@
       <c r="G169" t="n">
         <v>0.82</v>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>1</t>
@@ -11001,7 +10785,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11062,7 +10845,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11113,8 +10895,6 @@
       <c r="G172" t="n">
         <v>0.37</v>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>1</t>
@@ -11180,7 +10960,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11241,7 +11020,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11292,8 +11070,6 @@
       <c r="G175" t="n">
         <v>0.82</v>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>1</t>
@@ -11359,7 +11135,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11420,7 +11195,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11471,8 +11245,6 @@
       <c r="G178" t="n">
         <v>0.82</v>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>1</t>
@@ -11538,7 +11310,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11599,7 +11370,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11650,8 +11420,6 @@
       <c r="G181" t="n">
         <v>0.82</v>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>1</t>
@@ -11717,7 +11485,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11778,7 +11545,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11829,8 +11595,6 @@
       <c r="G184" t="n">
         <v>0.82</v>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>1</t>
@@ -11896,7 +11660,6 @@
           <t>0.955882</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11957,7 +11720,6 @@
           <t>0.044118</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12008,8 +11770,6 @@
       <c r="G187" t="n">
         <v>0.02</v>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>1</t>
@@ -12075,7 +11835,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12136,7 +11895,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12187,8 +11945,6 @@
       <c r="G190" t="n">
         <v>0.82</v>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>1</t>
@@ -12254,7 +12010,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12315,7 +12070,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12366,8 +12120,6 @@
       <c r="G193" t="n">
         <v>0.82</v>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>1</t>
@@ -12433,7 +12185,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12494,7 +12245,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12545,8 +12295,6 @@
       <c r="G196" t="n">
         <v>0.52</v>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>1</t>
@@ -12612,7 +12360,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12673,7 +12420,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12724,8 +12470,6 @@
       <c r="G199" t="n">
         <v>0.82</v>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>1</t>
@@ -12791,7 +12535,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12852,7 +12595,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12903,8 +12645,6 @@
       <c r="G202" t="n">
         <v>0.82</v>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>1</t>
@@ -12970,7 +12710,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13031,7 +12770,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13082,8 +12820,6 @@
       <c r="G205" t="n">
         <v>0.82</v>
       </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>1</t>
@@ -13149,7 +12885,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13210,7 +12945,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13261,8 +12995,6 @@
       <c r="G208" t="n">
         <v>0.82</v>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>1</t>
@@ -13328,7 +13060,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13389,7 +13120,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13440,8 +13170,6 @@
       <c r="G211" t="n">
         <v>0.37</v>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>1</t>
@@ -13507,7 +13235,6 @@
           <t>0.894444</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13568,7 +13295,6 @@
           <t>0.105556</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13619,8 +13345,6 @@
       <c r="G214" t="n">
         <v>0.17</v>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>1</t>
@@ -13686,7 +13410,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13747,7 +13470,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13798,8 +13520,6 @@
       <c r="G217" t="n">
         <v>0.82</v>
       </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>1</t>
@@ -13865,7 +13585,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13926,7 +13645,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13977,8 +13695,6 @@
       <c r="G220" t="n">
         <v>0.82</v>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>1</t>
@@ -14044,7 +13760,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14105,7 +13820,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14156,8 +13870,6 @@
       <c r="G223" t="n">
         <v>0.27</v>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>1</t>
@@ -14223,7 +13935,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14284,7 +13995,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14335,8 +14045,6 @@
       <c r="G226" t="n">
         <v>0.82</v>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>1</t>
@@ -14402,7 +14110,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14463,7 +14170,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -14514,8 +14220,6 @@
       <c r="G229" t="n">
         <v>0.37</v>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>1</t>
@@ -14581,7 +14285,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14632,8 +14335,6 @@
       <c r="G231" t="n">
         <v>0.15</v>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>1</t>
@@ -14699,7 +14400,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14750,8 +14450,6 @@
       <c r="G233" t="n">
         <v>0.1</v>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>1</t>
@@ -14817,7 +14515,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14868,8 +14565,6 @@
       <c r="G235" t="n">
         <v>0.15</v>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>1</t>
@@ -14935,7 +14630,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14986,8 +14680,6 @@
       <c r="G237" t="n">
         <v>0.1</v>
       </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>1</t>
@@ -15053,7 +14745,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15104,8 +14795,6 @@
       <c r="G239" t="n">
         <v>0.15</v>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>1</t>
@@ -15171,7 +14860,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15222,8 +14910,6 @@
       <c r="G241" t="n">
         <v>0.1</v>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>1</t>
@@ -15289,7 +14975,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15340,8 +15025,6 @@
       <c r="G243" t="n">
         <v>0.15</v>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>1</t>
@@ -15407,7 +15090,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15458,8 +15140,6 @@
       <c r="G245" t="n">
         <v>0.1</v>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>1</t>
@@ -15525,7 +15205,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15576,8 +15255,6 @@
       <c r="G247" t="n">
         <v>0.15</v>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>1</t>
@@ -15643,7 +15320,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15694,8 +15370,6 @@
       <c r="G249" t="n">
         <v>0.1</v>
       </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>1</t>
@@ -15761,7 +15435,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15812,8 +15485,6 @@
       <c r="G251" t="n">
         <v>0.15</v>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>1</t>
@@ -15879,7 +15550,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15930,8 +15600,6 @@
       <c r="G253" t="n">
         <v>0.1</v>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>1</t>
@@ -15997,7 +15665,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16048,8 +15715,6 @@
       <c r="G255" t="n">
         <v>0.15</v>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>1</t>
@@ -16115,7 +15780,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16166,8 +15830,6 @@
       <c r="G257" t="n">
         <v>0.1</v>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>1</t>
@@ -16233,7 +15895,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16284,8 +15945,6 @@
       <c r="G259" t="n">
         <v>0.1</v>
       </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>1</t>
@@ -16351,7 +16010,6 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16402,8 +16060,6 @@
       <c r="G261" t="n">
         <v>0.9</v>
       </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>1</t>
@@ -16469,7 +16125,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16520,8 +16175,6 @@
       <c r="G263" t="n">
         <v>0.15</v>
       </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>1</t>
@@ -16587,7 +16240,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16638,8 +16290,6 @@
       <c r="G265" t="n">
         <v>0.1</v>
       </c>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>1</t>
@@ -16705,7 +16355,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16756,8 +16405,6 @@
       <c r="G267" t="n">
         <v>0.15</v>
       </c>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>1</t>
@@ -16823,7 +16470,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16874,8 +16520,6 @@
       <c r="G269" t="n">
         <v>0.1</v>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>1</t>
@@ -16941,7 +16585,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16992,8 +16635,6 @@
       <c r="G271" t="n">
         <v>0.15</v>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>1</t>
@@ -17059,7 +16700,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17110,8 +16750,6 @@
       <c r="G273" t="n">
         <v>0.1</v>
       </c>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>1</t>
@@ -17177,7 +16815,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17228,8 +16865,6 @@
       <c r="G275" t="n">
         <v>0.15</v>
       </c>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>1</t>
@@ -17295,7 +16930,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17346,8 +16980,6 @@
       <c r="G277" t="n">
         <v>0.1</v>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>1</t>
@@ -17413,7 +17045,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17464,8 +17095,6 @@
       <c r="G279" t="n">
         <v>0.15</v>
       </c>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>1</t>
@@ -17531,7 +17160,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17582,8 +17210,6 @@
       <c r="G281" t="n">
         <v>0.1</v>
       </c>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>1</t>
@@ -17649,7 +17275,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17700,8 +17325,6 @@
       <c r="G283" t="n">
         <v>0.15</v>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>1</t>
@@ -17767,7 +17390,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17818,8 +17440,6 @@
       <c r="G285" t="n">
         <v>0.1</v>
       </c>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>1</t>
@@ -17885,7 +17505,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17936,8 +17555,6 @@
       <c r="G287" t="n">
         <v>0.15</v>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>1</t>
@@ -18003,7 +17620,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18054,8 +17670,6 @@
       <c r="G289" t="n">
         <v>0.1</v>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>1</t>
@@ -18121,7 +17735,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18172,8 +17785,6 @@
       <c r="G291" t="n">
         <v>0.15</v>
       </c>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>1</t>
@@ -18239,7 +17850,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18290,8 +17900,6 @@
       <c r="G293" t="n">
         <v>0.1</v>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>1</t>
@@ -18357,7 +17965,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18408,8 +18015,6 @@
       <c r="G295" t="n">
         <v>0.15</v>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>1</t>
@@ -18475,7 +18080,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18526,8 +18130,6 @@
       <c r="G297" t="n">
         <v>0.1</v>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>1</t>
@@ -18593,7 +18195,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18644,8 +18245,6 @@
       <c r="G299" t="n">
         <v>0.15</v>
       </c>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>1</t>
@@ -18711,7 +18310,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18762,8 +18360,6 @@
       <c r="G301" t="n">
         <v>0.1</v>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>1</t>
@@ -18829,7 +18425,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18880,8 +18475,6 @@
       <c r="G303" t="n">
         <v>0.15</v>
       </c>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>1</t>
@@ -18947,7 +18540,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18998,8 +18590,6 @@
       <c r="G305" t="n">
         <v>0.1</v>
       </c>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>1</t>
@@ -19065,7 +18655,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19116,8 +18705,6 @@
       <c r="G307" t="n">
         <v>0.15</v>
       </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>1</t>
@@ -19183,7 +18770,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19234,8 +18820,6 @@
       <c r="G309" t="n">
         <v>0.1</v>
       </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>1</t>
@@ -19301,7 +18885,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19352,8 +18935,6 @@
       <c r="G311" t="n">
         <v>0.15</v>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>1</t>
@@ -19419,7 +19000,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19470,8 +19050,6 @@
       <c r="G313" t="n">
         <v>0.1</v>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>1</t>
@@ -19537,7 +19115,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19588,8 +19165,6 @@
       <c r="G315" t="n">
         <v>0.15</v>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>1</t>
@@ -19655,7 +19230,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19706,8 +19280,6 @@
       <c r="G317" t="n">
         <v>0.1</v>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>1</t>
@@ -19773,7 +19345,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19824,8 +19395,6 @@
       <c r="G319" t="n">
         <v>0.15</v>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>1</t>
@@ -19891,7 +19460,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19942,8 +19510,6 @@
       <c r="G321" t="n">
         <v>0.1</v>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>1</t>
@@ -20009,7 +19575,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20060,8 +19625,6 @@
       <c r="G323" t="n">
         <v>0.15</v>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>1</t>
@@ -20127,7 +19690,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20178,8 +19740,6 @@
       <c r="G325" t="n">
         <v>0.1</v>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>1</t>
@@ -20245,7 +19805,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20296,8 +19855,6 @@
       <c r="G327" t="n">
         <v>0.15</v>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>1</t>
@@ -20363,7 +19920,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20414,8 +19970,6 @@
       <c r="G329" t="n">
         <v>0.1</v>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>1</t>
@@ -20481,7 +20035,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20532,8 +20085,6 @@
       <c r="G331" t="n">
         <v>0.15</v>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>1</t>
@@ -20599,7 +20150,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20650,8 +20200,6 @@
       <c r="G333" t="n">
         <v>0.1</v>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr">
         <is>
           <t>1</t>
@@ -20717,7 +20265,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20768,8 +20315,6 @@
       <c r="G335" t="n">
         <v>0.15</v>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr">
         <is>
           <t>1</t>
@@ -20835,7 +20380,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20886,8 +20430,6 @@
       <c r="G337" t="n">
         <v>0.1</v>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr">
         <is>
           <t>1</t>
@@ -20953,7 +20495,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21004,8 +20545,6 @@
       <c r="G339" t="n">
         <v>0.15</v>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
           <t>1</t>
@@ -21071,7 +20610,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21122,8 +20660,6 @@
       <c r="G341" t="n">
         <v>0.1</v>
       </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr">
         <is>
           <t>1</t>
@@ -21189,7 +20725,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21240,8 +20775,6 @@
       <c r="G343" t="n">
         <v>0.15</v>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr">
         <is>
           <t>1</t>
@@ -21307,7 +20840,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21358,8 +20890,6 @@
       <c r="G345" t="n">
         <v>0.1</v>
       </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr">
         <is>
           <t>1</t>
@@ -21425,7 +20955,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21476,8 +21005,6 @@
       <c r="G347" t="n">
         <v>0.15</v>
       </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr">
         <is>
           <t>1</t>
@@ -21543,7 +21070,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21594,8 +21120,6 @@
       <c r="G349" t="n">
         <v>0.1</v>
       </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr">
         <is>
           <t>1</t>
@@ -21661,7 +21185,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21712,8 +21235,6 @@
       <c r="G351" t="n">
         <v>0.15</v>
       </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr">
         <is>
           <t>1</t>
@@ -21779,7 +21300,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21830,8 +21350,6 @@
       <c r="G353" t="n">
         <v>0.1</v>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr">
         <is>
           <t>1</t>
@@ -21897,7 +21415,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21948,8 +21465,6 @@
       <c r="G355" t="n">
         <v>0.15</v>
       </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr">
         <is>
           <t>1</t>
@@ -22015,7 +21530,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22066,8 +21580,6 @@
       <c r="G357" t="n">
         <v>0.1</v>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
           <t>1</t>
@@ -22133,7 +21645,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22184,8 +21695,6 @@
       <c r="G359" t="n">
         <v>0.15</v>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr">
         <is>
           <t>1</t>
@@ -22251,7 +21760,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22302,8 +21810,6 @@
       <c r="G361" t="n">
         <v>0.1</v>
       </c>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr">
         <is>
           <t>1</t>
@@ -22369,7 +21875,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22420,8 +21925,6 @@
       <c r="G363" t="n">
         <v>0.15</v>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr">
         <is>
           <t>1</t>
@@ -22487,7 +21990,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22538,8 +22040,6 @@
       <c r="G365" t="n">
         <v>0.1</v>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr">
         <is>
           <t>1</t>
@@ -22605,7 +22105,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22656,8 +22155,6 @@
       <c r="G367" t="n">
         <v>0.15</v>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr">
         <is>
           <t>1</t>
@@ -22723,7 +22220,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22774,8 +22270,6 @@
       <c r="G369" t="n">
         <v>0.1</v>
       </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr">
         <is>
           <t>1</t>
@@ -22841,7 +22335,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22892,8 +22385,6 @@
       <c r="G371" t="n">
         <v>0.15</v>
       </c>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr">
         <is>
           <t>1</t>
@@ -22959,7 +22450,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23010,8 +22500,6 @@
       <c r="G373" t="n">
         <v>0.1</v>
       </c>
-      <c r="H373" t="inlineStr"/>
-      <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr">
         <is>
           <t>1</t>
@@ -23077,7 +22565,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23128,8 +22615,6 @@
       <c r="G375" t="n">
         <v>0.15</v>
       </c>
-      <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr">
         <is>
           <t>1</t>
@@ -23195,7 +22680,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23246,8 +22730,6 @@
       <c r="G377" t="n">
         <v>0.1</v>
       </c>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr">
         <is>
           <t>1</t>
@@ -23313,7 +22795,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23364,8 +22845,6 @@
       <c r="G379" t="n">
         <v>0.15</v>
       </c>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr">
         <is>
           <t>1</t>
@@ -23431,7 +22910,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23482,8 +22960,6 @@
       <c r="G381" t="n">
         <v>0.1</v>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr">
         <is>
           <t>1</t>
@@ -23549,7 +23025,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23600,8 +23075,6 @@
       <c r="G383" t="n">
         <v>0.15</v>
       </c>
-      <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr">
         <is>
           <t>1</t>
@@ -23667,7 +23140,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23718,8 +23190,6 @@
       <c r="G385" t="n">
         <v>0.1</v>
       </c>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr">
         <is>
           <t>1</t>
@@ -23785,7 +23255,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23836,8 +23305,6 @@
       <c r="G387" t="n">
         <v>0.15</v>
       </c>
-      <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr">
         <is>
           <t>1</t>
@@ -23903,7 +23370,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23954,8 +23420,6 @@
       <c r="G389" t="n">
         <v>0.1</v>
       </c>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
           <t>1</t>
@@ -24021,7 +23485,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24072,8 +23535,6 @@
       <c r="G391" t="n">
         <v>0.15</v>
       </c>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr">
         <is>
           <t>1</t>
@@ -24139,7 +23600,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24190,8 +23650,6 @@
       <c r="G393" t="n">
         <v>0.1</v>
       </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr">
         <is>
           <t>1</t>
@@ -24257,7 +23715,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24308,8 +23765,6 @@
       <c r="G395" t="n">
         <v>0.15</v>
       </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr">
         <is>
           <t>1</t>
@@ -24375,7 +23830,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24426,8 +23880,6 @@
       <c r="G397" t="n">
         <v>0.1</v>
       </c>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr">
         <is>
           <t>1</t>
@@ -24493,7 +23945,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24544,8 +23995,6 @@
       <c r="G399" t="n">
         <v>0.4</v>
       </c>
-      <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr">
         <is>
           <t>1</t>
@@ -24611,7 +24060,6 @@
           <t>0.44999999999999996</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24662,8 +24110,6 @@
       <c r="G401" t="n">
         <v>0.65</v>
       </c>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr">
         <is>
           <t>1</t>
@@ -24729,7 +24175,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24780,8 +24225,6 @@
       <c r="G403" t="n">
         <v>0.2</v>
       </c>
-      <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr">
         <is>
           <t>1</t>
@@ -24847,7 +24290,6 @@
           <t>0.65</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24898,8 +24340,6 @@
       <c r="G405" t="n">
         <v>0.45</v>
       </c>
-      <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr">
         <is>
           <t>1</t>
@@ -24965,7 +24405,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25016,8 +24455,6 @@
       <c r="G407" t="n">
         <v>0.4</v>
       </c>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
         <is>
           <t>1</t>
@@ -25083,7 +24520,6 @@
           <t>0.44999999999999996</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25134,8 +24570,6 @@
       <c r="G409" t="n">
         <v>0.65</v>
       </c>
-      <c r="H409" t="inlineStr"/>
-      <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr">
         <is>
           <t>1</t>
@@ -25201,7 +24635,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25252,8 +24685,6 @@
       <c r="G411" t="n">
         <v>0.4</v>
       </c>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr">
         <is>
           <t>1</t>
@@ -25319,7 +24750,6 @@
           <t>0.44999999999999996</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25370,8 +24800,6 @@
       <c r="G413" t="n">
         <v>0.65</v>
       </c>
-      <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr">
         <is>
           <t>1</t>
@@ -25437,7 +24865,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25488,8 +24915,6 @@
       <c r="G415" t="n">
         <v>0.4</v>
       </c>
-      <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr">
         <is>
           <t>1</t>
@@ -25555,7 +24980,6 @@
           <t>0.44999999999999996</t>
         </is>
       </c>
-      <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25606,8 +25030,6 @@
       <c r="G417" t="n">
         <v>0.65</v>
       </c>
-      <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr">
         <is>
           <t>1</t>
@@ -25673,7 +25095,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25724,8 +25145,6 @@
       <c r="G419" t="n">
         <v>0.15</v>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr">
         <is>
           <t>1</t>
@@ -25791,7 +25210,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25842,8 +25260,6 @@
       <c r="G421" t="n">
         <v>0.1</v>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr">
         <is>
           <t>1</t>
@@ -25909,7 +25325,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25960,8 +25375,6 @@
       <c r="G423" t="n">
         <v>0.15</v>
       </c>
-      <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr">
         <is>
           <t>1</t>
@@ -26027,7 +25440,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26078,8 +25490,6 @@
       <c r="G425" t="n">
         <v>0.1</v>
       </c>
-      <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr">
         <is>
           <t>1</t>
@@ -26145,7 +25555,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26196,8 +25605,6 @@
       <c r="G427" t="n">
         <v>0.15</v>
       </c>
-      <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr">
         <is>
           <t>1</t>
@@ -26263,7 +25670,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26314,8 +25720,6 @@
       <c r="G429" t="n">
         <v>0.1</v>
       </c>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr">
         <is>
           <t>1</t>
@@ -26381,7 +25785,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26432,8 +25835,6 @@
       <c r="G431" t="n">
         <v>0.15</v>
       </c>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr">
         <is>
           <t>1</t>
@@ -26499,7 +25900,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26550,8 +25950,6 @@
       <c r="G433" t="n">
         <v>0.1</v>
       </c>
-      <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr">
         <is>
           <t>1</t>
@@ -26617,7 +26015,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26668,8 +26065,6 @@
       <c r="G435" t="n">
         <v>0.15</v>
       </c>
-      <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr">
         <is>
           <t>1</t>
@@ -26735,7 +26130,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26786,8 +26180,6 @@
       <c r="G437" t="n">
         <v>0.1</v>
       </c>
-      <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr">
         <is>
           <t>1</t>
@@ -26853,7 +26245,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26904,8 +26295,6 @@
       <c r="G439" t="n">
         <v>0.15</v>
       </c>
-      <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr">
         <is>
           <t>1</t>
@@ -26971,7 +26360,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27022,8 +26410,6 @@
       <c r="G441" t="n">
         <v>0.1</v>
       </c>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr">
         <is>
           <t>1</t>
@@ -27089,7 +26475,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27140,8 +26525,6 @@
       <c r="G443" t="n">
         <v>0.15</v>
       </c>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr">
         <is>
           <t>1</t>
@@ -27207,7 +26590,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27258,8 +26640,6 @@
       <c r="G445" t="n">
         <v>0.1</v>
       </c>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr">
         <is>
           <t>1</t>
@@ -27325,7 +26705,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27376,8 +26755,6 @@
       <c r="G447" t="n">
         <v>0.15</v>
       </c>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr">
         <is>
           <t>1</t>
@@ -27443,7 +26820,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27494,8 +26870,6 @@
       <c r="G449" t="n">
         <v>0.1</v>
       </c>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr">
         <is>
           <t>1</t>
@@ -27561,7 +26935,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27612,8 +26985,6 @@
       <c r="G451" t="n">
         <v>0.15</v>
       </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr">
         <is>
           <t>1</t>
@@ -27679,7 +27050,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27730,8 +27100,6 @@
       <c r="G453" t="n">
         <v>0.1</v>
       </c>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr">
         <is>
           <t>1</t>
@@ -27797,7 +27165,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27848,8 +27215,6 @@
       <c r="G455" t="n">
         <v>0.15</v>
       </c>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr">
         <is>
           <t>1</t>
@@ -27915,7 +27280,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27966,8 +27330,6 @@
       <c r="G457" t="n">
         <v>0.1</v>
       </c>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr">
         <is>
           <t>1</t>
@@ -28033,7 +27395,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28084,8 +27445,6 @@
       <c r="G459" t="n">
         <v>0.15</v>
       </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr">
         <is>
           <t>1</t>
@@ -28151,7 +27510,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28202,8 +27560,6 @@
       <c r="G461" t="n">
         <v>0.1</v>
       </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr">
         <is>
           <t>1</t>
@@ -28269,7 +27625,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28320,8 +27675,6 @@
       <c r="G463" t="n">
         <v>0.15</v>
       </c>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr">
         <is>
           <t>1</t>
@@ -28387,7 +27740,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28438,8 +27790,6 @@
       <c r="G465" t="n">
         <v>0.1</v>
       </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr">
         <is>
           <t>1</t>
@@ -28505,7 +27855,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28556,8 +27905,6 @@
       <c r="G467" t="n">
         <v>0.15</v>
       </c>
-      <c r="H467" t="inlineStr"/>
-      <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr">
         <is>
           <t>1</t>
@@ -28623,7 +27970,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28674,8 +28020,6 @@
       <c r="G469" t="n">
         <v>0.1</v>
       </c>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr">
         <is>
           <t>1</t>
@@ -28741,7 +28085,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28792,8 +28135,6 @@
       <c r="G471" t="n">
         <v>0.15</v>
       </c>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr">
         <is>
           <t>1</t>
@@ -28859,7 +28200,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28910,8 +28250,6 @@
       <c r="G473" t="n">
         <v>0.1</v>
       </c>
-      <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr">
         <is>
           <t>1</t>
@@ -28977,7 +28315,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29028,8 +28365,6 @@
       <c r="G475" t="n">
         <v>0.15</v>
       </c>
-      <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
         <is>
           <t>1</t>
@@ -29095,7 +28430,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29146,8 +28480,6 @@
       <c r="G477" t="n">
         <v>0.1</v>
       </c>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr">
         <is>
           <t>1</t>
@@ -29213,7 +28545,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29264,8 +28595,6 @@
       <c r="G479" t="n">
         <v>0.15</v>
       </c>
-      <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr">
         <is>
           <t>1</t>
@@ -29331,7 +28660,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29382,8 +28710,6 @@
       <c r="G481" t="n">
         <v>0.1</v>
       </c>
-      <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr">
         <is>
           <t>1</t>
@@ -29449,7 +28775,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29500,8 +28825,6 @@
       <c r="G483" t="n">
         <v>0.15</v>
       </c>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr">
         <is>
           <t>1</t>
@@ -29567,7 +28890,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29618,8 +28940,6 @@
       <c r="G485" t="n">
         <v>0.1</v>
       </c>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr">
         <is>
           <t>1</t>
@@ -29685,7 +29005,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29736,8 +29055,6 @@
       <c r="G487" t="n">
         <v>0.15</v>
       </c>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
           <t>1</t>
@@ -29803,7 +29120,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29854,8 +29170,6 @@
       <c r="G489" t="n">
         <v>0.1</v>
       </c>
-      <c r="H489" t="inlineStr"/>
-      <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr">
         <is>
           <t>1</t>
@@ -29921,7 +29235,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29972,8 +29285,6 @@
       <c r="G491" t="n">
         <v>0.15</v>
       </c>
-      <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr">
         <is>
           <t>1</t>
@@ -30039,7 +29350,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30090,8 +29400,6 @@
       <c r="G493" t="n">
         <v>0.1</v>
       </c>
-      <c r="H493" t="inlineStr"/>
-      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr">
         <is>
           <t>1</t>
@@ -30157,7 +29465,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30208,8 +29515,6 @@
       <c r="G495" t="n">
         <v>0.15</v>
       </c>
-      <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr">
         <is>
           <t>1</t>
@@ -30275,7 +29580,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30326,8 +29630,6 @@
       <c r="G497" t="n">
         <v>0.1</v>
       </c>
-      <c r="H497" t="inlineStr"/>
-      <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr">
         <is>
           <t>1</t>
@@ -30393,7 +29695,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30444,8 +29745,6 @@
       <c r="G499" t="n">
         <v>0.15</v>
       </c>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr">
         <is>
           <t>1</t>
@@ -30511,7 +29810,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30562,8 +29860,6 @@
       <c r="G501" t="n">
         <v>0.1</v>
       </c>
-      <c r="H501" t="inlineStr"/>
-      <c r="I501" t="inlineStr"/>
       <c r="J501" t="inlineStr">
         <is>
           <t>1</t>
@@ -30629,7 +29925,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30680,8 +29975,6 @@
       <c r="G503" t="n">
         <v>0.15</v>
       </c>
-      <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr">
         <is>
           <t>1</t>
@@ -30747,7 +30040,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30798,8 +30090,6 @@
       <c r="G505" t="n">
         <v>0.1</v>
       </c>
-      <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr">
         <is>
           <t>1</t>
@@ -30865,7 +30155,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30916,8 +30205,6 @@
       <c r="G507" t="n">
         <v>0.15</v>
       </c>
-      <c r="H507" t="inlineStr"/>
-      <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr">
         <is>
           <t>1</t>
@@ -30983,7 +30270,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31034,8 +30320,6 @@
       <c r="G509" t="n">
         <v>0.1</v>
       </c>
-      <c r="H509" t="inlineStr"/>
-      <c r="I509" t="inlineStr"/>
       <c r="J509" t="inlineStr">
         <is>
           <t>1</t>
@@ -31101,7 +30385,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31152,8 +30435,6 @@
       <c r="G511" t="n">
         <v>0.15</v>
       </c>
-      <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr"/>
       <c r="J511" t="inlineStr">
         <is>
           <t>1</t>
@@ -31219,7 +30500,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31270,8 +30550,6 @@
       <c r="G513" t="n">
         <v>0.1</v>
       </c>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr">
         <is>
           <t>1</t>
@@ -31337,7 +30615,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31388,8 +30665,6 @@
       <c r="G515" t="n">
         <v>0.15</v>
       </c>
-      <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr">
         <is>
           <t>1</t>
@@ -31455,7 +30730,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31506,8 +30780,6 @@
       <c r="G517" t="n">
         <v>0.1</v>
       </c>
-      <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
       <c r="J517" t="inlineStr">
         <is>
           <t>1</t>
@@ -31573,7 +30845,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31624,8 +30895,6 @@
       <c r="G519" t="n">
         <v>0.15</v>
       </c>
-      <c r="H519" t="inlineStr"/>
-      <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr">
         <is>
           <t>1</t>
@@ -31691,7 +30960,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31742,8 +31010,6 @@
       <c r="G521" t="n">
         <v>0.1</v>
       </c>
-      <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr">
         <is>
           <t>1</t>
@@ -31809,7 +31075,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31860,8 +31125,6 @@
       <c r="G523" t="n">
         <v>0.15</v>
       </c>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr"/>
       <c r="J523" t="inlineStr">
         <is>
           <t>1</t>
@@ -31927,7 +31190,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31978,8 +31240,6 @@
       <c r="G525" t="n">
         <v>0.1</v>
       </c>
-      <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr"/>
       <c r="J525" t="inlineStr">
         <is>
           <t>1</t>
@@ -32045,7 +31305,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32096,8 +31355,6 @@
       <c r="G527" t="n">
         <v>0.15</v>
       </c>
-      <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr"/>
       <c r="J527" t="inlineStr">
         <is>
           <t>1</t>
@@ -32163,7 +31420,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32214,8 +31470,6 @@
       <c r="G529" t="n">
         <v>0.1</v>
       </c>
-      <c r="H529" t="inlineStr"/>
-      <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr">
         <is>
           <t>1</t>
@@ -32281,7 +31535,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32332,8 +31585,6 @@
       <c r="G531" t="n">
         <v>0.15</v>
       </c>
-      <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr"/>
       <c r="J531" t="inlineStr">
         <is>
           <t>1</t>
@@ -32399,7 +31650,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32450,8 +31700,6 @@
       <c r="G533" t="n">
         <v>0.1</v>
       </c>
-      <c r="H533" t="inlineStr"/>
-      <c r="I533" t="inlineStr"/>
       <c r="J533" t="inlineStr">
         <is>
           <t>1</t>
@@ -32517,7 +31765,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32568,8 +31815,6 @@
       <c r="G535" t="n">
         <v>0.15</v>
       </c>
-      <c r="H535" t="inlineStr"/>
-      <c r="I535" t="inlineStr"/>
       <c r="J535" t="inlineStr">
         <is>
           <t>1</t>
@@ -32635,7 +31880,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32686,8 +31930,6 @@
       <c r="G537" t="n">
         <v>0.1</v>
       </c>
-      <c r="H537" t="inlineStr"/>
-      <c r="I537" t="inlineStr"/>
       <c r="J537" t="inlineStr">
         <is>
           <t>1</t>
@@ -32753,7 +31995,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32804,8 +32045,6 @@
       <c r="G539" t="n">
         <v>0.15</v>
       </c>
-      <c r="H539" t="inlineStr"/>
-      <c r="I539" t="inlineStr"/>
       <c r="J539" t="inlineStr">
         <is>
           <t>1</t>
@@ -32871,7 +32110,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32922,8 +32160,6 @@
       <c r="G541" t="n">
         <v>0.1</v>
       </c>
-      <c r="H541" t="inlineStr"/>
-      <c r="I541" t="inlineStr"/>
       <c r="J541" t="inlineStr">
         <is>
           <t>1</t>
@@ -32989,7 +32225,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33040,8 +32275,6 @@
       <c r="G543" t="n">
         <v>0.15</v>
       </c>
-      <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr"/>
       <c r="J543" t="inlineStr">
         <is>
           <t>1</t>
@@ -33107,7 +32340,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33158,8 +32390,6 @@
       <c r="G545" t="n">
         <v>0.1</v>
       </c>
-      <c r="H545" t="inlineStr"/>
-      <c r="I545" t="inlineStr"/>
       <c r="J545" t="inlineStr">
         <is>
           <t>1</t>
@@ -33225,7 +32455,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33276,8 +32505,6 @@
       <c r="G547" t="n">
         <v>0.15</v>
       </c>
-      <c r="H547" t="inlineStr"/>
-      <c r="I547" t="inlineStr"/>
       <c r="J547" t="inlineStr">
         <is>
           <t>1</t>
@@ -33343,7 +32570,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33394,8 +32620,6 @@
       <c r="G549" t="n">
         <v>0.1</v>
       </c>
-      <c r="H549" t="inlineStr"/>
-      <c r="I549" t="inlineStr"/>
       <c r="J549" t="inlineStr">
         <is>
           <t>1</t>
@@ -33461,7 +32685,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33512,8 +32735,6 @@
       <c r="G551" t="n">
         <v>0.15</v>
       </c>
-      <c r="H551" t="inlineStr"/>
-      <c r="I551" t="inlineStr"/>
       <c r="J551" t="inlineStr">
         <is>
           <t>1</t>
@@ -33579,7 +32800,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33630,8 +32850,6 @@
       <c r="G553" t="n">
         <v>0.1</v>
       </c>
-      <c r="H553" t="inlineStr"/>
-      <c r="I553" t="inlineStr"/>
       <c r="J553" t="inlineStr">
         <is>
           <t>1</t>
@@ -33697,7 +32915,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33748,8 +32965,6 @@
       <c r="G555" t="n">
         <v>0.15</v>
       </c>
-      <c r="H555" t="inlineStr"/>
-      <c r="I555" t="inlineStr"/>
       <c r="J555" t="inlineStr">
         <is>
           <t>1</t>
@@ -33815,7 +33030,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33866,8 +33080,6 @@
       <c r="G557" t="n">
         <v>0.1</v>
       </c>
-      <c r="H557" t="inlineStr"/>
-      <c r="I557" t="inlineStr"/>
       <c r="J557" t="inlineStr">
         <is>
           <t>1</t>
@@ -33933,7 +33145,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33984,8 +33195,6 @@
       <c r="G559" t="n">
         <v>0.15</v>
       </c>
-      <c r="H559" t="inlineStr"/>
-      <c r="I559" t="inlineStr"/>
       <c r="J559" t="inlineStr">
         <is>
           <t>1</t>
@@ -34051,7 +33260,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34102,8 +33310,6 @@
       <c r="G561" t="n">
         <v>0.1</v>
       </c>
-      <c r="H561" t="inlineStr"/>
-      <c r="I561" t="inlineStr"/>
       <c r="J561" t="inlineStr">
         <is>
           <t>1</t>
@@ -34169,7 +33375,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34220,8 +33425,6 @@
       <c r="G563" t="n">
         <v>0.15</v>
       </c>
-      <c r="H563" t="inlineStr"/>
-      <c r="I563" t="inlineStr"/>
       <c r="J563" t="inlineStr">
         <is>
           <t>1</t>
@@ -34287,7 +33490,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34338,8 +33540,6 @@
       <c r="G565" t="n">
         <v>0.1</v>
       </c>
-      <c r="H565" t="inlineStr"/>
-      <c r="I565" t="inlineStr"/>
       <c r="J565" t="inlineStr">
         <is>
           <t>1</t>
@@ -34405,7 +33605,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34456,8 +33655,6 @@
       <c r="G567" t="n">
         <v>0.15</v>
       </c>
-      <c r="H567" t="inlineStr"/>
-      <c r="I567" t="inlineStr"/>
       <c r="J567" t="inlineStr">
         <is>
           <t>1</t>
@@ -34523,7 +33720,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34574,8 +33770,6 @@
       <c r="G569" t="n">
         <v>0.1</v>
       </c>
-      <c r="H569" t="inlineStr"/>
-      <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr">
         <is>
           <t>1</t>
@@ -34641,7 +33835,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34692,8 +33885,6 @@
       <c r="G571" t="n">
         <v>0.15</v>
       </c>
-      <c r="H571" t="inlineStr"/>
-      <c r="I571" t="inlineStr"/>
       <c r="J571" t="inlineStr">
         <is>
           <t>1</t>
@@ -34759,7 +33950,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34810,8 +34000,6 @@
       <c r="G573" t="n">
         <v>0.1</v>
       </c>
-      <c r="H573" t="inlineStr"/>
-      <c r="I573" t="inlineStr"/>
       <c r="J573" t="inlineStr">
         <is>
           <t>1</t>
@@ -34877,7 +34065,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34928,8 +34115,6 @@
       <c r="G575" t="n">
         <v>0.15</v>
       </c>
-      <c r="H575" t="inlineStr"/>
-      <c r="I575" t="inlineStr"/>
       <c r="J575" t="inlineStr">
         <is>
           <t>1</t>
@@ -34995,7 +34180,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35046,8 +34230,6 @@
       <c r="G577" t="n">
         <v>0.1</v>
       </c>
-      <c r="H577" t="inlineStr"/>
-      <c r="I577" t="inlineStr"/>
       <c r="J577" t="inlineStr">
         <is>
           <t>1</t>
@@ -35113,7 +34295,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35164,8 +34345,6 @@
       <c r="G579" t="n">
         <v>0.15</v>
       </c>
-      <c r="H579" t="inlineStr"/>
-      <c r="I579" t="inlineStr"/>
       <c r="J579" t="inlineStr">
         <is>
           <t>1</t>
@@ -35231,7 +34410,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35282,8 +34460,6 @@
       <c r="G581" t="n">
         <v>0.1</v>
       </c>
-      <c r="H581" t="inlineStr"/>
-      <c r="I581" t="inlineStr"/>
       <c r="J581" t="inlineStr">
         <is>
           <t>1</t>
@@ -35349,7 +34525,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35400,8 +34575,6 @@
       <c r="G583" t="n">
         <v>0.15</v>
       </c>
-      <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr"/>
       <c r="J583" t="inlineStr">
         <is>
           <t>1</t>
@@ -35467,7 +34640,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35518,8 +34690,6 @@
       <c r="G585" t="n">
         <v>0.1</v>
       </c>
-      <c r="H585" t="inlineStr"/>
-      <c r="I585" t="inlineStr"/>
       <c r="J585" t="inlineStr">
         <is>
           <t>1</t>
@@ -35585,7 +34755,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35636,8 +34805,6 @@
       <c r="G587" t="n">
         <v>0.15</v>
       </c>
-      <c r="H587" t="inlineStr"/>
-      <c r="I587" t="inlineStr"/>
       <c r="J587" t="inlineStr">
         <is>
           <t>1</t>
@@ -35703,7 +34870,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35754,8 +34920,6 @@
       <c r="G589" t="n">
         <v>0.1</v>
       </c>
-      <c r="H589" t="inlineStr"/>
-      <c r="I589" t="inlineStr"/>
       <c r="J589" t="inlineStr">
         <is>
           <t>1</t>
@@ -35821,7 +34985,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35872,8 +35035,6 @@
       <c r="G591" t="n">
         <v>0.15</v>
       </c>
-      <c r="H591" t="inlineStr"/>
-      <c r="I591" t="inlineStr"/>
       <c r="J591" t="inlineStr">
         <is>
           <t>1</t>
@@ -35939,7 +35100,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35990,8 +35150,6 @@
       <c r="G593" t="n">
         <v>0.1</v>
       </c>
-      <c r="H593" t="inlineStr"/>
-      <c r="I593" t="inlineStr"/>
       <c r="J593" t="inlineStr">
         <is>
           <t>1</t>
@@ -36057,7 +35215,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36108,8 +35265,6 @@
       <c r="G595" t="n">
         <v>0.15</v>
       </c>
-      <c r="H595" t="inlineStr"/>
-      <c r="I595" t="inlineStr"/>
       <c r="J595" t="inlineStr">
         <is>
           <t>1</t>
@@ -36175,7 +35330,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36226,8 +35380,6 @@
       <c r="G597" t="n">
         <v>0.1</v>
       </c>
-      <c r="H597" t="inlineStr"/>
-      <c r="I597" t="inlineStr"/>
       <c r="J597" t="inlineStr">
         <is>
           <t>1</t>
@@ -36293,7 +35445,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36344,8 +35495,6 @@
       <c r="G599" t="n">
         <v>0.15</v>
       </c>
-      <c r="H599" t="inlineStr"/>
-      <c r="I599" t="inlineStr"/>
       <c r="J599" t="inlineStr">
         <is>
           <t>1</t>
@@ -36411,7 +35560,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36462,8 +35610,6 @@
       <c r="G601" t="n">
         <v>0.1</v>
       </c>
-      <c r="H601" t="inlineStr"/>
-      <c r="I601" t="inlineStr"/>
       <c r="J601" t="inlineStr">
         <is>
           <t>1</t>
@@ -36529,7 +35675,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36580,8 +35725,6 @@
       <c r="G603" t="n">
         <v>0.15</v>
       </c>
-      <c r="H603" t="inlineStr"/>
-      <c r="I603" t="inlineStr"/>
       <c r="J603" t="inlineStr">
         <is>
           <t>1</t>
@@ -36647,7 +35790,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36698,8 +35840,6 @@
       <c r="G605" t="n">
         <v>0.1</v>
       </c>
-      <c r="H605" t="inlineStr"/>
-      <c r="I605" t="inlineStr"/>
       <c r="J605" t="inlineStr">
         <is>
           <t>1</t>
@@ -36765,7 +35905,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36816,8 +35955,6 @@
       <c r="G607" t="n">
         <v>0.15</v>
       </c>
-      <c r="H607" t="inlineStr"/>
-      <c r="I607" t="inlineStr"/>
       <c r="J607" t="inlineStr">
         <is>
           <t>1</t>
@@ -36883,7 +36020,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36934,8 +36070,6 @@
       <c r="G609" t="n">
         <v>0.1</v>
       </c>
-      <c r="H609" t="inlineStr"/>
-      <c r="I609" t="inlineStr"/>
       <c r="J609" t="inlineStr">
         <is>
           <t>1</t>
@@ -37001,7 +36135,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -37052,8 +36185,6 @@
       <c r="G611" t="n">
         <v>0.15</v>
       </c>
-      <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
       <c r="J611" t="inlineStr">
         <is>
           <t>1</t>
@@ -37119,7 +36250,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
           <t>separation</t>
@@ -37170,8 +36300,6 @@
       <c r="G613" t="n">
         <v>0.1</v>
       </c>
-      <c r="H613" t="inlineStr"/>
-      <c r="I613" t="inlineStr"/>
       <c r="J613" t="inlineStr">
         <is>
           <t>1</t>
@@ -37237,7 +36365,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -37288,8 +36415,6 @@
       <c r="G615" t="n">
         <v>0.15</v>
       </c>
-      <c r="H615" t="inlineStr"/>
-      <c r="I615" t="inlineStr"/>
       <c r="J615" t="inlineStr">
         <is>
           <t>1</t>
@@ -37355,7 +36480,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
           <t>separation</t>
@@ -37406,8 +36530,6 @@
       <c r="G617" t="n">
         <v>0.1</v>
       </c>
-      <c r="H617" t="inlineStr"/>
-      <c r="I617" t="inlineStr"/>
       <c r="J617" t="inlineStr">
         <is>
           <t>1</t>
@@ -37473,7 +36595,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -37524,8 +36645,6 @@
       <c r="G619" t="n">
         <v>0.15</v>
       </c>
-      <c r="H619" t="inlineStr"/>
-      <c r="I619" t="inlineStr"/>
       <c r="J619" t="inlineStr">
         <is>
           <t>1</t>
@@ -37591,7 +36710,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
           <t>separation</t>
@@ -37642,8 +36760,6 @@
       <c r="G621" t="n">
         <v>0.1</v>
       </c>
-      <c r="H621" t="inlineStr"/>
-      <c r="I621" t="inlineStr"/>
       <c r="J621" t="inlineStr">
         <is>
           <t>1</t>
@@ -37709,7 +36825,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -37760,8 +36875,6 @@
       <c r="G623" t="n">
         <v>0.15</v>
       </c>
-      <c r="H623" t="inlineStr"/>
-      <c r="I623" t="inlineStr"/>
       <c r="J623" t="inlineStr">
         <is>
           <t>1</t>
@@ -37827,7 +36940,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
           <t>separation</t>
@@ -37878,8 +36990,6 @@
       <c r="G625" t="n">
         <v>0.1</v>
       </c>
-      <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr"/>
       <c r="J625" t="inlineStr">
         <is>
           <t>1</t>
@@ -37945,7 +37055,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -37996,8 +37105,6 @@
       <c r="G627" t="n">
         <v>0.2</v>
       </c>
-      <c r="H627" t="inlineStr"/>
-      <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr">
         <is>
           <t>1</t>
@@ -38063,7 +37170,6 @@
           <t>0.65</t>
         </is>
       </c>
-      <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
           <t>separation</t>
@@ -38114,8 +37220,6 @@
       <c r="G629" t="n">
         <v>0.45</v>
       </c>
-      <c r="H629" t="inlineStr"/>
-      <c r="I629" t="inlineStr"/>
       <c r="J629" t="inlineStr">
         <is>
           <t>1</t>
@@ -38181,7 +37285,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -38232,8 +37335,6 @@
       <c r="G631" t="n">
         <v>0.4</v>
       </c>
-      <c r="H631" t="inlineStr"/>
-      <c r="I631" t="inlineStr"/>
       <c r="J631" t="inlineStr">
         <is>
           <t>1</t>
@@ -38299,7 +37400,6 @@
           <t>0.44999999999999996</t>
         </is>
       </c>
-      <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
           <t>separation</t>
@@ -38350,8 +37450,6 @@
       <c r="G633" t="n">
         <v>0.65</v>
       </c>
-      <c r="H633" t="inlineStr"/>
-      <c r="I633" t="inlineStr"/>
       <c r="J633" t="inlineStr">
         <is>
           <t>1</t>
@@ -38370,6 +37468,41 @@
       <c r="M633" t="inlineStr">
         <is>
           <t>derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>child_layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>material</t>
         </is>
       </c>
     </row>

--- a/data_folder/carcomposition_mockup/input_data/case.xlsx
+++ b/data_folder/carcomposition_mockup/input_data/case.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,12 +434,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -513,7 +523,6 @@
           <t>material_suffix</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -521,7 +530,6 @@
           <t>groups</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -564,37 +572,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>keyed_at</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>is_loss</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -875,67 +883,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Input_layer</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Input_layer_key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>TC_target_key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>value_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_max</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_residual</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>

--- a/data_folder/carcomposition_mockup/input_data/case.xlsx
+++ b/data_folder/carcomposition_mockup/input_data/case.xlsx
@@ -559,16 +559,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,11 +598,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_loss</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>role</t>
         </is>
       </c>
@@ -634,10 +628,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>intermediate</t>
         </is>
@@ -669,10 +660,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>intermediate</t>
         </is>
@@ -704,10 +692,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
@@ -739,10 +724,7 @@
           <t>material</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>recovered</t>
         </is>
@@ -774,10 +756,7 @@
           <t>material</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
@@ -809,10 +788,7 @@
           <t>material</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>recovered</t>
         </is>
@@ -844,10 +820,7 @@
           <t>material</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>loss</t>
         </is>

--- a/data_folder/carcomposition_mockup/input_data/case.xlsx
+++ b/data_folder/carcomposition_mockup/input_data/case.xlsx
@@ -827,6 +827,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="E2:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$B$2:$B$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$C$2:$C$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37463,7 +37471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37472,6 +37480,16 @@
           <t>child_layer</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>keyed_at</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37479,11 +37497,50 @@
           <t>element</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>material</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>handoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>intermediate</t>
         </is>
       </c>
     </row>

--- a/data_folder/carcomposition_mockup/input_data/case.xlsx
+++ b/data_folder/carcomposition_mockup/input_data/case.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,6 +523,7 @@
           <t>material_suffix</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -530,6 +531,7 @@
           <t>groups</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -539,7 +541,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -970,7 +972,6 @@
       <c r="I2" t="n">
         <v>0.3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1027,7 +1028,6 @@
       <c r="I3" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1078,9 +1078,6 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1137,7 +1134,6 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1194,7 +1190,6 @@
       <c r="I6" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1245,9 +1240,6 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1304,7 +1296,6 @@
       <c r="I8" t="n">
         <v>0.3</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1361,7 +1352,6 @@
       <c r="I9" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1412,9 +1402,6 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1471,7 +1458,6 @@
       <c r="I11" t="n">
         <v>0.3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1528,7 +1514,6 @@
       <c r="I12" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1579,9 +1564,6 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1638,7 +1620,6 @@
       <c r="I14" t="n">
         <v>0.3</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1695,7 +1676,6 @@
       <c r="I15" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1746,9 +1726,6 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1805,7 +1782,6 @@
       <c r="I17" t="n">
         <v>0.6</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1862,7 +1838,6 @@
       <c r="I18" t="n">
         <v>0.6625</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1913,9 +1888,6 @@
       <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -1972,7 +1944,6 @@
       <c r="I20" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2029,7 +2000,6 @@
       <c r="I21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2080,9 +2050,6 @@
       <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2139,7 +2106,6 @@
       <c r="I23" t="n">
         <v>0.3</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2196,7 +2162,6 @@
       <c r="I24" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2247,9 +2212,6 @@
       <c r="G25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2306,7 +2268,6 @@
       <c r="I26" t="n">
         <v>0.3</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2363,7 +2324,6 @@
       <c r="I27" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2414,9 +2374,6 @@
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2473,7 +2430,6 @@
       <c r="I29" t="n">
         <v>0.85</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2530,7 +2486,6 @@
       <c r="I30" t="n">
         <v>0.475</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2581,9 +2536,6 @@
       <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2640,7 +2592,6 @@
       <c r="I32" t="n">
         <v>0.3</v>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2697,7 +2648,6 @@
       <c r="I33" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2748,9 +2698,6 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2807,7 +2754,6 @@
       <c r="I35" t="n">
         <v>0.75</v>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2864,7 +2810,6 @@
       <c r="I36" t="n">
         <v>0.55</v>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -2915,9 +2860,6 @@
       <c r="G37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -2974,7 +2916,6 @@
       <c r="I38" t="n">
         <v>0.3</v>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3031,7 +2972,6 @@
       <c r="I39" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3082,9 +3022,6 @@
       <c r="G40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3141,7 +3078,6 @@
       <c r="I41" t="n">
         <v>0.3</v>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3198,7 +3134,6 @@
       <c r="I42" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3249,9 +3184,6 @@
       <c r="G43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3308,7 +3240,6 @@
       <c r="I44" t="n">
         <v>1</v>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3365,7 +3296,6 @@
       <c r="I45" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3416,9 +3346,6 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3475,7 +3402,6 @@
       <c r="I47" t="n">
         <v>0.3</v>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3532,7 +3458,6 @@
       <c r="I48" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3583,9 +3508,6 @@
       <c r="G49" t="n">
         <v>1</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3642,7 +3564,6 @@
       <c r="I50" t="n">
         <v>0.3</v>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3699,7 +3620,6 @@
       <c r="I51" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3750,9 +3670,6 @@
       <c r="G52" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3809,7 +3726,6 @@
       <c r="I53" t="n">
         <v>0.6</v>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3866,7 +3782,6 @@
       <c r="I54" t="n">
         <v>0.6625</v>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -3917,9 +3832,6 @@
       <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -3976,7 +3888,6 @@
       <c r="I56" t="n">
         <v>0.3</v>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4033,7 +3944,6 @@
       <c r="I57" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4084,9 +3994,6 @@
       <c r="G58" t="n">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4143,7 +4050,6 @@
       <c r="I59" t="n">
         <v>0.3</v>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4200,7 +4106,6 @@
       <c r="I60" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4251,9 +4156,6 @@
       <c r="G61" t="n">
         <v>1</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4310,7 +4212,6 @@
       <c r="I62" t="n">
         <v>0.3</v>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4367,7 +4268,6 @@
       <c r="I63" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4418,9 +4318,6 @@
       <c r="G64" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4477,7 +4374,6 @@
       <c r="I65" t="n">
         <v>0.3</v>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4534,7 +4430,6 @@
       <c r="I66" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4585,9 +4480,6 @@
       <c r="G67" t="n">
         <v>1</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4644,7 +4536,6 @@
       <c r="I68" t="n">
         <v>0.75</v>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4701,7 +4592,6 @@
       <c r="I69" t="n">
         <v>0.55</v>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4752,9 +4642,6 @@
       <c r="G70" t="n">
         <v>1</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4811,7 +4698,6 @@
       <c r="I71" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4868,7 +4754,6 @@
       <c r="I72" t="n">
         <v>0.4</v>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -4919,9 +4804,6 @@
       <c r="G73" t="n">
         <v>1</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -4978,7 +4860,6 @@
       <c r="I74" t="n">
         <v>0.3</v>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5035,7 +4916,6 @@
       <c r="I75" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5086,9 +4966,6 @@
       <c r="G76" t="n">
         <v>1</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5145,7 +5022,6 @@
       <c r="I77" t="n">
         <v>0.3</v>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5202,7 +5078,6 @@
       <c r="I78" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5253,9 +5128,6 @@
       <c r="G79" t="n">
         <v>1</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5312,7 +5184,6 @@
       <c r="I80" t="n">
         <v>0.85</v>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5369,7 +5240,6 @@
       <c r="I81" t="n">
         <v>0.475</v>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5420,9 +5290,6 @@
       <c r="G82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5479,7 +5346,6 @@
       <c r="I83" t="n">
         <v>0.3</v>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5536,7 +5402,6 @@
       <c r="I84" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5587,9 +5452,6 @@
       <c r="G85" t="n">
         <v>1</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5646,7 +5508,6 @@
       <c r="I86" t="n">
         <v>0.75</v>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5703,7 +5564,6 @@
       <c r="I87" t="n">
         <v>0.55</v>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5754,9 +5614,6 @@
       <c r="G88" t="n">
         <v>1</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5813,7 +5670,6 @@
       <c r="I89" t="n">
         <v>0.3</v>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5870,7 +5726,6 @@
       <c r="I90" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -5921,9 +5776,6 @@
       <c r="G91" t="n">
         <v>1</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -5980,7 +5832,6 @@
       <c r="I92" t="n">
         <v>1</v>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6037,7 +5888,6 @@
       <c r="I93" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6088,9 +5938,6 @@
       <c r="G94" t="n">
         <v>1</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6147,7 +5994,6 @@
       <c r="I95" t="n">
         <v>0.3</v>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6204,7 +6050,6 @@
       <c r="I96" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6255,9 +6100,6 @@
       <c r="G97" t="n">
         <v>1</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6314,7 +6156,6 @@
       <c r="I98" t="n">
         <v>1</v>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6371,7 +6212,6 @@
       <c r="I99" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6422,9 +6262,6 @@
       <c r="G100" t="n">
         <v>1</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6481,7 +6318,6 @@
       <c r="I101" t="n">
         <v>0.3</v>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6538,7 +6374,6 @@
       <c r="I102" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6589,9 +6424,6 @@
       <c r="G103" t="n">
         <v>1</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6648,7 +6480,6 @@
       <c r="I104" t="n">
         <v>0.3</v>
       </c>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6705,7 +6536,6 @@
       <c r="I105" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6756,9 +6586,6 @@
       <c r="G106" t="n">
         <v>1</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6815,7 +6642,6 @@
       <c r="I107" t="n">
         <v>0.6</v>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6872,7 +6698,6 @@
       <c r="I108" t="n">
         <v>0.6625</v>
       </c>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -6923,9 +6748,6 @@
       <c r="G109" t="n">
         <v>1</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -6982,7 +6804,6 @@
       <c r="I110" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7039,7 +6860,6 @@
       <c r="I111" t="n">
         <v>0.4</v>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7090,9 +6910,6 @@
       <c r="G112" t="n">
         <v>1</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7149,7 +6966,6 @@
       <c r="I113" t="n">
         <v>0.3</v>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7206,7 +7022,6 @@
       <c r="I114" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7257,9 +7072,6 @@
       <c r="G115" t="n">
         <v>1</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7316,7 +7128,6 @@
       <c r="I116" t="n">
         <v>0.3</v>
       </c>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7373,7 +7184,6 @@
       <c r="I117" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7424,9 +7234,6 @@
       <c r="G118" t="n">
         <v>1</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7483,7 +7290,6 @@
       <c r="I119" t="n">
         <v>0.85</v>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7540,7 +7346,6 @@
       <c r="I120" t="n">
         <v>0.475</v>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7591,9 +7396,6 @@
       <c r="G121" t="n">
         <v>1</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7650,7 +7452,6 @@
       <c r="I122" t="n">
         <v>0.3</v>
       </c>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7707,7 +7508,6 @@
       <c r="I123" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7758,9 +7558,6 @@
       <c r="G124" t="n">
         <v>1</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7817,7 +7614,6 @@
       <c r="I125" t="n">
         <v>0.75</v>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7874,7 +7670,6 @@
       <c r="I126" t="n">
         <v>0.55</v>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -7925,9 +7720,6 @@
       <c r="G127" t="n">
         <v>1</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -7984,7 +7776,6 @@
       <c r="I128" t="n">
         <v>0.3</v>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8041,7 +7832,6 @@
       <c r="I129" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8092,9 +7882,6 @@
       <c r="G130" t="n">
         <v>1</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8151,7 +7938,6 @@
       <c r="I131" t="n">
         <v>0.3</v>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8208,7 +7994,6 @@
       <c r="I132" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8259,9 +8044,6 @@
       <c r="G133" t="n">
         <v>1</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8318,7 +8100,6 @@
       <c r="I134" t="n">
         <v>0.3</v>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8375,7 +8156,6 @@
       <c r="I135" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8426,9 +8206,6 @@
       <c r="G136" t="n">
         <v>1</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8485,7 +8262,6 @@
       <c r="I137" t="n">
         <v>1</v>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8542,7 +8318,6 @@
       <c r="I138" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8593,9 +8368,6 @@
       <c r="G139" t="n">
         <v>1</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8652,7 +8424,6 @@
       <c r="I140" t="n">
         <v>0.3</v>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8709,7 +8480,6 @@
       <c r="I141" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8760,9 +8530,6 @@
       <c r="G142" t="n">
         <v>1</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8819,7 +8586,6 @@
       <c r="I143" t="n">
         <v>1</v>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8876,7 +8642,6 @@
       <c r="I144" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -8927,9 +8692,6 @@
       <c r="G145" t="n">
         <v>1</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -8986,7 +8748,6 @@
       <c r="I146" t="n">
         <v>0.3</v>
       </c>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9043,7 +8804,6 @@
       <c r="I147" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9094,9 +8854,6 @@
       <c r="G148" t="n">
         <v>1</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9153,7 +8910,6 @@
       <c r="I149" t="n">
         <v>0.3</v>
       </c>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9210,7 +8966,6 @@
       <c r="I150" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9261,9 +9016,6 @@
       <c r="G151" t="n">
         <v>1</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9320,7 +9072,6 @@
       <c r="I152" t="n">
         <v>0.6</v>
       </c>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9377,7 +9128,6 @@
       <c r="I153" t="n">
         <v>0.6625</v>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9428,9 +9178,6 @@
       <c r="G154" t="n">
         <v>1</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9487,7 +9234,6 @@
       <c r="I155" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9544,7 +9290,6 @@
       <c r="I156" t="n">
         <v>0.4</v>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9595,9 +9340,6 @@
       <c r="G157" t="n">
         <v>1</v>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9654,7 +9396,6 @@
       <c r="I158" t="n">
         <v>0.3</v>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9711,7 +9452,6 @@
       <c r="I159" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9762,9 +9502,6 @@
       <c r="G160" t="n">
         <v>1</v>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9821,7 +9558,6 @@
       <c r="I161" t="n">
         <v>0.3</v>
       </c>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9878,7 +9614,6 @@
       <c r="I162" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -9929,9 +9664,6 @@
       <c r="G163" t="n">
         <v>1</v>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -9988,7 +9720,6 @@
       <c r="I164" t="n">
         <v>0.85</v>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10045,7 +9776,6 @@
       <c r="I165" t="n">
         <v>0.475</v>
       </c>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10096,9 +9826,6 @@
       <c r="G166" t="n">
         <v>1</v>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10155,7 +9882,6 @@
       <c r="I167" t="n">
         <v>0.3</v>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10212,7 +9938,6 @@
       <c r="I168" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10263,9 +9988,6 @@
       <c r="G169" t="n">
         <v>1</v>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10322,7 +10044,6 @@
       <c r="I170" t="n">
         <v>0.75</v>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10379,7 +10100,6 @@
       <c r="I171" t="n">
         <v>0.55</v>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10430,9 +10150,6 @@
       <c r="G172" t="n">
         <v>1</v>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10489,7 +10206,6 @@
       <c r="I173" t="n">
         <v>0.3</v>
       </c>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10546,7 +10262,6 @@
       <c r="I174" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10597,9 +10312,6 @@
       <c r="G175" t="n">
         <v>1</v>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10656,7 +10368,6 @@
       <c r="I176" t="n">
         <v>0.3</v>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10713,7 +10424,6 @@
       <c r="I177" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10764,9 +10474,6 @@
       <c r="G178" t="n">
         <v>1</v>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10823,7 +10530,6 @@
       <c r="I179" t="n">
         <v>0.3</v>
       </c>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10880,7 +10586,6 @@
       <c r="I180" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -10931,9 +10636,6 @@
       <c r="G181" t="n">
         <v>1</v>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -10990,7 +10692,6 @@
       <c r="I182" t="n">
         <v>0.3</v>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11047,7 +10748,6 @@
       <c r="I183" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11098,9 +10798,6 @@
       <c r="G184" t="n">
         <v>1</v>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11157,7 +10854,6 @@
       <c r="I185" t="n">
         <v>1</v>
       </c>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11214,7 +10910,6 @@
       <c r="I186" t="n">
         <v>0.2875</v>
       </c>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11265,9 +10960,6 @@
       <c r="G187" t="n">
         <v>1</v>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11324,7 +11016,6 @@
       <c r="I188" t="n">
         <v>0.3</v>
       </c>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11381,7 +11072,6 @@
       <c r="I189" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11432,9 +11122,6 @@
       <c r="G190" t="n">
         <v>1</v>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11491,7 +11178,6 @@
       <c r="I191" t="n">
         <v>0.3</v>
       </c>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11548,7 +11234,6 @@
       <c r="I192" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11599,9 +11284,6 @@
       <c r="G193" t="n">
         <v>1</v>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11658,7 +11340,6 @@
       <c r="I194" t="n">
         <v>0.6</v>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11715,7 +11396,6 @@
       <c r="I195" t="n">
         <v>0.6625</v>
       </c>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11766,9 +11446,6 @@
       <c r="G196" t="n">
         <v>1</v>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11825,7 +11502,6 @@
       <c r="I197" t="n">
         <v>0.3</v>
       </c>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11882,7 +11558,6 @@
       <c r="I198" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -11933,9 +11608,6 @@
       <c r="G199" t="n">
         <v>1</v>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -11992,7 +11664,6 @@
       <c r="I200" t="n">
         <v>0.3</v>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12049,7 +11720,6 @@
       <c r="I201" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12100,9 +11770,6 @@
       <c r="G202" t="n">
         <v>1</v>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12159,7 +11826,6 @@
       <c r="I203" t="n">
         <v>0.3</v>
       </c>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12216,7 +11882,6 @@
       <c r="I204" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12267,9 +11932,6 @@
       <c r="G205" t="n">
         <v>1</v>
       </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12326,7 +11988,6 @@
       <c r="I206" t="n">
         <v>0.3</v>
       </c>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12383,7 +12044,6 @@
       <c r="I207" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12434,9 +12094,6 @@
       <c r="G208" t="n">
         <v>1</v>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12493,7 +12150,6 @@
       <c r="I209" t="n">
         <v>0.75</v>
       </c>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12550,7 +12206,6 @@
       <c r="I210" t="n">
         <v>0.55</v>
       </c>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12601,9 +12256,6 @@
       <c r="G211" t="n">
         <v>1</v>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12660,7 +12312,6 @@
       <c r="I212" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12717,7 +12368,6 @@
       <c r="I213" t="n">
         <v>0.4</v>
       </c>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12768,9 +12418,6 @@
       <c r="G214" t="n">
         <v>1</v>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12827,7 +12474,6 @@
       <c r="I215" t="n">
         <v>0.3</v>
       </c>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12884,7 +12530,6 @@
       <c r="I216" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -12935,9 +12580,6 @@
       <c r="G217" t="n">
         <v>1</v>
       </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -12994,7 +12636,6 @@
       <c r="I218" t="n">
         <v>0.3</v>
       </c>
-      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13051,7 +12692,6 @@
       <c r="I219" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13102,9 +12742,6 @@
       <c r="G220" t="n">
         <v>1</v>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -13161,7 +12798,6 @@
       <c r="I221" t="n">
         <v>0.85</v>
       </c>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13218,7 +12854,6 @@
       <c r="I222" t="n">
         <v>0.475</v>
       </c>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13269,9 +12904,6 @@
       <c r="G223" t="n">
         <v>1</v>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -13328,7 +12960,6 @@
       <c r="I224" t="n">
         <v>0.3</v>
       </c>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13385,7 +13016,6 @@
       <c r="I225" t="n">
         <v>0.8875</v>
       </c>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13436,9 +13066,6 @@
       <c r="G226" t="n">
         <v>1</v>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -13495,7 +13122,6 @@
       <c r="I227" t="n">
         <v>0.75</v>
       </c>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13552,7 +13178,6 @@
       <c r="I228" t="n">
         <v>0.55</v>
       </c>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -13603,9 +13228,6 @@
       <c r="G229" t="n">
         <v>1</v>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>hulk_transfer</t>
@@ -13662,7 +13284,6 @@
       <c r="I230" t="n">
         <v>0.95</v>
       </c>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -13719,7 +13340,6 @@
       <c r="I231" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -13776,7 +13396,6 @@
       <c r="I232" t="n">
         <v>1</v>
       </c>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>separation</t>
@@ -13833,7 +13452,6 @@
       <c r="I233" t="n">
         <v>0.325</v>
       </c>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>separation</t>
@@ -13890,7 +13508,6 @@
       <c r="I234" t="n">
         <v>0.95</v>
       </c>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -13947,7 +13564,6 @@
       <c r="I235" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14004,7 +13620,6 @@
       <c r="I236" t="n">
         <v>1</v>
       </c>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14061,7 +13676,6 @@
       <c r="I237" t="n">
         <v>0.325</v>
       </c>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14118,7 +13732,6 @@
       <c r="I238" t="n">
         <v>0.95</v>
       </c>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14175,7 +13788,6 @@
       <c r="I239" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14232,7 +13844,6 @@
       <c r="I240" t="n">
         <v>1</v>
       </c>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14289,7 +13900,6 @@
       <c r="I241" t="n">
         <v>0.325</v>
       </c>
-      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14346,7 +13956,6 @@
       <c r="I242" t="n">
         <v>0.95</v>
       </c>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14403,7 +14012,6 @@
       <c r="I243" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14460,7 +14068,6 @@
       <c r="I244" t="n">
         <v>1</v>
       </c>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14517,7 +14124,6 @@
       <c r="I245" t="n">
         <v>0.325</v>
       </c>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14574,7 +14180,6 @@
       <c r="I246" t="n">
         <v>0.95</v>
       </c>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14631,7 +14236,6 @@
       <c r="I247" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14688,7 +14292,6 @@
       <c r="I248" t="n">
         <v>1</v>
       </c>
-      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14745,7 +14348,6 @@
       <c r="I249" t="n">
         <v>0.325</v>
       </c>
-      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14802,7 +14404,6 @@
       <c r="I250" t="n">
         <v>0.95</v>
       </c>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14859,7 +14460,6 @@
       <c r="I251" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -14916,7 +14516,6 @@
       <c r="I252" t="n">
         <v>1</v>
       </c>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>separation</t>
@@ -14973,7 +14572,6 @@
       <c r="I253" t="n">
         <v>0.325</v>
       </c>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15030,7 +14628,6 @@
       <c r="I254" t="n">
         <v>0.95</v>
       </c>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15087,7 +14684,6 @@
       <c r="I255" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15144,7 +14740,6 @@
       <c r="I256" t="n">
         <v>1</v>
       </c>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15201,7 +14796,6 @@
       <c r="I257" t="n">
         <v>0.325</v>
       </c>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15258,7 +14852,6 @@
       <c r="I258" t="n">
         <v>1</v>
       </c>
-      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15315,7 +14908,6 @@
       <c r="I259" t="n">
         <v>0.325</v>
       </c>
-      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15372,7 +14964,6 @@
       <c r="I260" t="n">
         <v>0.2</v>
       </c>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15429,7 +15020,6 @@
       <c r="I261" t="n">
         <v>0.925</v>
       </c>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15486,7 +15076,6 @@
       <c r="I262" t="n">
         <v>0.95</v>
       </c>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15543,7 +15132,6 @@
       <c r="I263" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15600,7 +15188,6 @@
       <c r="I264" t="n">
         <v>1</v>
       </c>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15657,7 +15244,6 @@
       <c r="I265" t="n">
         <v>0.325</v>
       </c>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15714,7 +15300,6 @@
       <c r="I266" t="n">
         <v>0.95</v>
       </c>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15771,7 +15356,6 @@
       <c r="I267" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15828,7 +15412,6 @@
       <c r="I268" t="n">
         <v>1</v>
       </c>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15885,7 +15468,6 @@
       <c r="I269" t="n">
         <v>0.325</v>
       </c>
-      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
           <t>separation</t>
@@ -15942,7 +15524,6 @@
       <c r="I270" t="n">
         <v>0.95</v>
       </c>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -15999,7 +15580,6 @@
       <c r="I271" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16056,7 +15636,6 @@
       <c r="I272" t="n">
         <v>1</v>
       </c>
-      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16113,7 +15692,6 @@
       <c r="I273" t="n">
         <v>0.325</v>
       </c>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16170,7 +15748,6 @@
       <c r="I274" t="n">
         <v>0.95</v>
       </c>
-      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16227,7 +15804,6 @@
       <c r="I275" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16284,7 +15860,6 @@
       <c r="I276" t="n">
         <v>1</v>
       </c>
-      <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16341,7 +15916,6 @@
       <c r="I277" t="n">
         <v>0.325</v>
       </c>
-      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16398,7 +15972,6 @@
       <c r="I278" t="n">
         <v>0.95</v>
       </c>
-      <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16455,7 +16028,6 @@
       <c r="I279" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16512,7 +16084,6 @@
       <c r="I280" t="n">
         <v>1</v>
       </c>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16569,7 +16140,6 @@
       <c r="I281" t="n">
         <v>0.325</v>
       </c>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16626,7 +16196,6 @@
       <c r="I282" t="n">
         <v>0.95</v>
       </c>
-      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16683,7 +16252,6 @@
       <c r="I283" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16740,7 +16308,6 @@
       <c r="I284" t="n">
         <v>1</v>
       </c>
-      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16797,7 +16364,6 @@
       <c r="I285" t="n">
         <v>0.325</v>
       </c>
-      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
           <t>separation</t>
@@ -16854,7 +16420,6 @@
       <c r="I286" t="n">
         <v>0.95</v>
       </c>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16911,7 +16476,6 @@
       <c r="I287" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -16968,7 +16532,6 @@
       <c r="I288" t="n">
         <v>1</v>
       </c>
-      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17025,7 +16588,6 @@
       <c r="I289" t="n">
         <v>0.325</v>
       </c>
-      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17082,7 +16644,6 @@
       <c r="I290" t="n">
         <v>0.95</v>
       </c>
-      <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17139,7 +16700,6 @@
       <c r="I291" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17196,7 +16756,6 @@
       <c r="I292" t="n">
         <v>1</v>
       </c>
-      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17253,7 +16812,6 @@
       <c r="I293" t="n">
         <v>0.325</v>
       </c>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17310,7 +16868,6 @@
       <c r="I294" t="n">
         <v>0.95</v>
       </c>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17367,7 +16924,6 @@
       <c r="I295" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17424,7 +16980,6 @@
       <c r="I296" t="n">
         <v>1</v>
       </c>
-      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17481,7 +17036,6 @@
       <c r="I297" t="n">
         <v>0.325</v>
       </c>
-      <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17538,7 +17092,6 @@
       <c r="I298" t="n">
         <v>0.95</v>
       </c>
-      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17595,7 +17148,6 @@
       <c r="I299" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17652,7 +17204,6 @@
       <c r="I300" t="n">
         <v>1</v>
       </c>
-      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17709,7 +17260,6 @@
       <c r="I301" t="n">
         <v>0.325</v>
       </c>
-      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17766,7 +17316,6 @@
       <c r="I302" t="n">
         <v>0.95</v>
       </c>
-      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17823,7 +17372,6 @@
       <c r="I303" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -17880,7 +17428,6 @@
       <c r="I304" t="n">
         <v>1</v>
       </c>
-      <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17937,7 +17484,6 @@
       <c r="I305" t="n">
         <v>0.325</v>
       </c>
-      <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
           <t>separation</t>
@@ -17994,7 +17540,6 @@
       <c r="I306" t="n">
         <v>0.95</v>
       </c>
-      <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18051,7 +17596,6 @@
       <c r="I307" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18108,7 +17652,6 @@
       <c r="I308" t="n">
         <v>1</v>
       </c>
-      <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18165,7 +17708,6 @@
       <c r="I309" t="n">
         <v>0.325</v>
       </c>
-      <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18222,7 +17764,6 @@
       <c r="I310" t="n">
         <v>0.95</v>
       </c>
-      <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18279,7 +17820,6 @@
       <c r="I311" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18336,7 +17876,6 @@
       <c r="I312" t="n">
         <v>1</v>
       </c>
-      <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18393,7 +17932,6 @@
       <c r="I313" t="n">
         <v>0.325</v>
       </c>
-      <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18450,7 +17988,6 @@
       <c r="I314" t="n">
         <v>0.95</v>
       </c>
-      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18507,7 +18044,6 @@
       <c r="I315" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18564,7 +18100,6 @@
       <c r="I316" t="n">
         <v>1</v>
       </c>
-      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18621,7 +18156,6 @@
       <c r="I317" t="n">
         <v>0.325</v>
       </c>
-      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18678,7 +18212,6 @@
       <c r="I318" t="n">
         <v>0.95</v>
       </c>
-      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18735,7 +18268,6 @@
       <c r="I319" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18792,7 +18324,6 @@
       <c r="I320" t="n">
         <v>1</v>
       </c>
-      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18849,7 +18380,6 @@
       <c r="I321" t="n">
         <v>0.325</v>
       </c>
-      <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
           <t>separation</t>
@@ -18906,7 +18436,6 @@
       <c r="I322" t="n">
         <v>0.95</v>
       </c>
-      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -18963,7 +18492,6 @@
       <c r="I323" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19020,7 +18548,6 @@
       <c r="I324" t="n">
         <v>1</v>
       </c>
-      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19077,7 +18604,6 @@
       <c r="I325" t="n">
         <v>0.325</v>
       </c>
-      <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19134,7 +18660,6 @@
       <c r="I326" t="n">
         <v>0.95</v>
       </c>
-      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19191,7 +18716,6 @@
       <c r="I327" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19248,7 +18772,6 @@
       <c r="I328" t="n">
         <v>1</v>
       </c>
-      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19305,7 +18828,6 @@
       <c r="I329" t="n">
         <v>0.325</v>
       </c>
-      <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19362,7 +18884,6 @@
       <c r="I330" t="n">
         <v>0.95</v>
       </c>
-      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19419,7 +18940,6 @@
       <c r="I331" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19476,7 +18996,6 @@
       <c r="I332" t="n">
         <v>1</v>
       </c>
-      <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19533,7 +19052,6 @@
       <c r="I333" t="n">
         <v>0.325</v>
       </c>
-      <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19590,7 +19108,6 @@
       <c r="I334" t="n">
         <v>0.95</v>
       </c>
-      <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19647,7 +19164,6 @@
       <c r="I335" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19704,7 +19220,6 @@
       <c r="I336" t="n">
         <v>1</v>
       </c>
-      <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19761,7 +19276,6 @@
       <c r="I337" t="n">
         <v>0.325</v>
       </c>
-      <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19818,7 +19332,6 @@
       <c r="I338" t="n">
         <v>0.95</v>
       </c>
-      <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19875,7 +19388,6 @@
       <c r="I339" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -19932,7 +19444,6 @@
       <c r="I340" t="n">
         <v>1</v>
       </c>
-      <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
           <t>separation</t>
@@ -19989,7 +19500,6 @@
       <c r="I341" t="n">
         <v>0.325</v>
       </c>
-      <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20046,7 +19556,6 @@
       <c r="I342" t="n">
         <v>0.95</v>
       </c>
-      <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20103,7 +19612,6 @@
       <c r="I343" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20160,7 +19668,6 @@
       <c r="I344" t="n">
         <v>1</v>
       </c>
-      <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20217,7 +19724,6 @@
       <c r="I345" t="n">
         <v>0.325</v>
       </c>
-      <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20274,7 +19780,6 @@
       <c r="I346" t="n">
         <v>0.95</v>
       </c>
-      <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20331,7 +19836,6 @@
       <c r="I347" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20388,7 +19892,6 @@
       <c r="I348" t="n">
         <v>1</v>
       </c>
-      <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20445,7 +19948,6 @@
       <c r="I349" t="n">
         <v>0.325</v>
       </c>
-      <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20502,7 +20004,6 @@
       <c r="I350" t="n">
         <v>0.95</v>
       </c>
-      <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20559,7 +20060,6 @@
       <c r="I351" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20616,7 +20116,6 @@
       <c r="I352" t="n">
         <v>1</v>
       </c>
-      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20673,7 +20172,6 @@
       <c r="I353" t="n">
         <v>0.325</v>
       </c>
-      <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20730,7 +20228,6 @@
       <c r="I354" t="n">
         <v>0.95</v>
       </c>
-      <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20787,7 +20284,6 @@
       <c r="I355" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -20844,7 +20340,6 @@
       <c r="I356" t="n">
         <v>1</v>
       </c>
-      <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20901,7 +20396,6 @@
       <c r="I357" t="n">
         <v>0.325</v>
       </c>
-      <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
           <t>separation</t>
@@ -20958,7 +20452,6 @@
       <c r="I358" t="n">
         <v>0.95</v>
       </c>
-      <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21015,7 +20508,6 @@
       <c r="I359" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21072,7 +20564,6 @@
       <c r="I360" t="n">
         <v>1</v>
       </c>
-      <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21129,7 +20620,6 @@
       <c r="I361" t="n">
         <v>0.325</v>
       </c>
-      <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21186,7 +20676,6 @@
       <c r="I362" t="n">
         <v>0.95</v>
       </c>
-      <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21243,7 +20732,6 @@
       <c r="I363" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21300,7 +20788,6 @@
       <c r="I364" t="n">
         <v>1</v>
       </c>
-      <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21357,7 +20844,6 @@
       <c r="I365" t="n">
         <v>0.325</v>
       </c>
-      <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21414,7 +20900,6 @@
       <c r="I366" t="n">
         <v>0.95</v>
       </c>
-      <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21471,7 +20956,6 @@
       <c r="I367" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21528,7 +21012,6 @@
       <c r="I368" t="n">
         <v>1</v>
       </c>
-      <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21585,7 +21068,6 @@
       <c r="I369" t="n">
         <v>0.325</v>
       </c>
-      <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21642,7 +21124,6 @@
       <c r="I370" t="n">
         <v>0.95</v>
       </c>
-      <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21699,7 +21180,6 @@
       <c r="I371" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21756,7 +21236,6 @@
       <c r="I372" t="n">
         <v>1</v>
       </c>
-      <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21813,7 +21292,6 @@
       <c r="I373" t="n">
         <v>0.325</v>
       </c>
-      <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
           <t>separation</t>
@@ -21870,7 +21348,6 @@
       <c r="I374" t="n">
         <v>0.95</v>
       </c>
-      <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21927,7 +21404,6 @@
       <c r="I375" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -21984,7 +21460,6 @@
       <c r="I376" t="n">
         <v>1</v>
       </c>
-      <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22041,7 +21516,6 @@
       <c r="I377" t="n">
         <v>0.325</v>
       </c>
-      <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22098,7 +21572,6 @@
       <c r="I378" t="n">
         <v>0.95</v>
       </c>
-      <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22155,7 +21628,6 @@
       <c r="I379" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22212,7 +21684,6 @@
       <c r="I380" t="n">
         <v>1</v>
       </c>
-      <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22269,7 +21740,6 @@
       <c r="I381" t="n">
         <v>0.325</v>
       </c>
-      <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22326,7 +21796,6 @@
       <c r="I382" t="n">
         <v>0.95</v>
       </c>
-      <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22383,7 +21852,6 @@
       <c r="I383" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22440,7 +21908,6 @@
       <c r="I384" t="n">
         <v>1</v>
       </c>
-      <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22497,7 +21964,6 @@
       <c r="I385" t="n">
         <v>0.325</v>
       </c>
-      <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22554,7 +22020,6 @@
       <c r="I386" t="n">
         <v>0.95</v>
       </c>
-      <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22611,7 +22076,6 @@
       <c r="I387" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22668,7 +22132,6 @@
       <c r="I388" t="n">
         <v>1</v>
       </c>
-      <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22725,7 +22188,6 @@
       <c r="I389" t="n">
         <v>0.325</v>
       </c>
-      <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22782,7 +22244,6 @@
       <c r="I390" t="n">
         <v>0.95</v>
       </c>
-      <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22839,7 +22300,6 @@
       <c r="I391" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -22896,7 +22356,6 @@
       <c r="I392" t="n">
         <v>1</v>
       </c>
-      <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
           <t>separation</t>
@@ -22953,7 +22412,6 @@
       <c r="I393" t="n">
         <v>0.325</v>
       </c>
-      <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23010,7 +22468,6 @@
       <c r="I394" t="n">
         <v>0.95</v>
       </c>
-      <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23067,7 +22524,6 @@
       <c r="I395" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23124,7 +22580,6 @@
       <c r="I396" t="n">
         <v>1</v>
       </c>
-      <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23181,7 +22636,6 @@
       <c r="I397" t="n">
         <v>0.325</v>
       </c>
-      <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23238,7 +22692,6 @@
       <c r="I398" t="n">
         <v>0.7</v>
       </c>
-      <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23295,7 +22748,6 @@
       <c r="I399" t="n">
         <v>0.55</v>
       </c>
-      <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23352,7 +22804,6 @@
       <c r="I400" t="n">
         <v>0.45</v>
       </c>
-      <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23409,7 +22860,6 @@
       <c r="I401" t="n">
         <v>0.7375</v>
       </c>
-      <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23466,7 +22916,6 @@
       <c r="I402" t="n">
         <v>0.9</v>
       </c>
-      <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23523,7 +22972,6 @@
       <c r="I403" t="n">
         <v>0.4</v>
       </c>
-      <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23580,7 +23028,6 @@
       <c r="I404" t="n">
         <v>0.65</v>
       </c>
-      <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23637,7 +23084,6 @@
       <c r="I405" t="n">
         <v>0.5875</v>
       </c>
-      <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23694,7 +23140,6 @@
       <c r="I406" t="n">
         <v>0.7</v>
       </c>
-      <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23751,7 +23196,6 @@
       <c r="I407" t="n">
         <v>0.55</v>
       </c>
-      <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23808,7 +23252,6 @@
       <c r="I408" t="n">
         <v>0.45</v>
       </c>
-      <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23865,7 +23308,6 @@
       <c r="I409" t="n">
         <v>0.7375</v>
       </c>
-      <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
           <t>separation</t>
@@ -23922,7 +23364,6 @@
       <c r="I410" t="n">
         <v>0.7</v>
       </c>
-      <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -23979,7 +23420,6 @@
       <c r="I411" t="n">
         <v>0.55</v>
       </c>
-      <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24036,7 +23476,6 @@
       <c r="I412" t="n">
         <v>0.45</v>
       </c>
-      <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24093,7 +23532,6 @@
       <c r="I413" t="n">
         <v>0.7375</v>
       </c>
-      <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24150,7 +23588,6 @@
       <c r="I414" t="n">
         <v>0.7</v>
       </c>
-      <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24207,7 +23644,6 @@
       <c r="I415" t="n">
         <v>0.55</v>
       </c>
-      <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24264,7 +23700,6 @@
       <c r="I416" t="n">
         <v>0.45</v>
       </c>
-      <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24321,7 +23756,6 @@
       <c r="I417" t="n">
         <v>0.7375</v>
       </c>
-      <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24378,7 +23812,6 @@
       <c r="I418" t="n">
         <v>0.95</v>
       </c>
-      <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24435,7 +23868,6 @@
       <c r="I419" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24492,7 +23924,6 @@
       <c r="I420" t="n">
         <v>1</v>
       </c>
-      <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24549,7 +23980,6 @@
       <c r="I421" t="n">
         <v>0.325</v>
       </c>
-      <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24606,7 +24036,6 @@
       <c r="I422" t="n">
         <v>0.95</v>
       </c>
-      <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24663,7 +24092,6 @@
       <c r="I423" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24720,7 +24148,6 @@
       <c r="I424" t="n">
         <v>1</v>
       </c>
-      <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24777,7 +24204,6 @@
       <c r="I425" t="n">
         <v>0.325</v>
       </c>
-      <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
           <t>separation</t>
@@ -24834,7 +24260,6 @@
       <c r="I426" t="n">
         <v>0.95</v>
       </c>
-      <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24891,7 +24316,6 @@
       <c r="I427" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -24948,7 +24372,6 @@
       <c r="I428" t="n">
         <v>1</v>
       </c>
-      <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25005,7 +24428,6 @@
       <c r="I429" t="n">
         <v>0.325</v>
       </c>
-      <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25062,7 +24484,6 @@
       <c r="I430" t="n">
         <v>0.95</v>
       </c>
-      <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25119,7 +24540,6 @@
       <c r="I431" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25176,7 +24596,6 @@
       <c r="I432" t="n">
         <v>1</v>
       </c>
-      <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25233,7 +24652,6 @@
       <c r="I433" t="n">
         <v>0.325</v>
       </c>
-      <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25290,7 +24708,6 @@
       <c r="I434" t="n">
         <v>0.95</v>
       </c>
-      <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25347,7 +24764,6 @@
       <c r="I435" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25404,7 +24820,6 @@
       <c r="I436" t="n">
         <v>1</v>
       </c>
-      <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25461,7 +24876,6 @@
       <c r="I437" t="n">
         <v>0.325</v>
       </c>
-      <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25518,7 +24932,6 @@
       <c r="I438" t="n">
         <v>0.95</v>
       </c>
-      <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25575,7 +24988,6 @@
       <c r="I439" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25632,7 +25044,6 @@
       <c r="I440" t="n">
         <v>1</v>
       </c>
-      <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25689,7 +25100,6 @@
       <c r="I441" t="n">
         <v>0.325</v>
       </c>
-      <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25746,7 +25156,6 @@
       <c r="I442" t="n">
         <v>0.95</v>
       </c>
-      <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25803,7 +25212,6 @@
       <c r="I443" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -25860,7 +25268,6 @@
       <c r="I444" t="n">
         <v>1</v>
       </c>
-      <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25917,7 +25324,6 @@
       <c r="I445" t="n">
         <v>0.325</v>
       </c>
-      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
           <t>separation</t>
@@ -25974,7 +25380,6 @@
       <c r="I446" t="n">
         <v>0.95</v>
       </c>
-      <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26031,7 +25436,6 @@
       <c r="I447" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26088,7 +25492,6 @@
       <c r="I448" t="n">
         <v>1</v>
       </c>
-      <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26145,7 +25548,6 @@
       <c r="I449" t="n">
         <v>0.325</v>
       </c>
-      <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26202,7 +25604,6 @@
       <c r="I450" t="n">
         <v>0.95</v>
       </c>
-      <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26259,7 +25660,6 @@
       <c r="I451" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26316,7 +25716,6 @@
       <c r="I452" t="n">
         <v>1</v>
       </c>
-      <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26373,7 +25772,6 @@
       <c r="I453" t="n">
         <v>0.325</v>
       </c>
-      <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26430,7 +25828,6 @@
       <c r="I454" t="n">
         <v>0.95</v>
       </c>
-      <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26487,7 +25884,6 @@
       <c r="I455" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26544,7 +25940,6 @@
       <c r="I456" t="n">
         <v>1</v>
       </c>
-      <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26601,7 +25996,6 @@
       <c r="I457" t="n">
         <v>0.325</v>
       </c>
-      <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26658,7 +26052,6 @@
       <c r="I458" t="n">
         <v>0.95</v>
       </c>
-      <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26715,7 +26108,6 @@
       <c r="I459" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26772,7 +26164,6 @@
       <c r="I460" t="n">
         <v>1</v>
       </c>
-      <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26829,7 +26220,6 @@
       <c r="I461" t="n">
         <v>0.325</v>
       </c>
-      <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
           <t>separation</t>
@@ -26886,7 +26276,6 @@
       <c r="I462" t="n">
         <v>0.95</v>
       </c>
-      <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -26943,7 +26332,6 @@
       <c r="I463" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27000,7 +26388,6 @@
       <c r="I464" t="n">
         <v>1</v>
       </c>
-      <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27057,7 +26444,6 @@
       <c r="I465" t="n">
         <v>0.325</v>
       </c>
-      <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27114,7 +26500,6 @@
       <c r="I466" t="n">
         <v>0.95</v>
       </c>
-      <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27171,7 +26556,6 @@
       <c r="I467" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27228,7 +26612,6 @@
       <c r="I468" t="n">
         <v>1</v>
       </c>
-      <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27285,7 +26668,6 @@
       <c r="I469" t="n">
         <v>0.325</v>
       </c>
-      <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27342,7 +26724,6 @@
       <c r="I470" t="n">
         <v>0.95</v>
       </c>
-      <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27399,7 +26780,6 @@
       <c r="I471" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27456,7 +26836,6 @@
       <c r="I472" t="n">
         <v>1</v>
       </c>
-      <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27513,7 +26892,6 @@
       <c r="I473" t="n">
         <v>0.325</v>
       </c>
-      <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27570,7 +26948,6 @@
       <c r="I474" t="n">
         <v>0.95</v>
       </c>
-      <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27627,7 +27004,6 @@
       <c r="I475" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27684,7 +27060,6 @@
       <c r="I476" t="n">
         <v>1</v>
       </c>
-      <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27741,7 +27116,6 @@
       <c r="I477" t="n">
         <v>0.325</v>
       </c>
-      <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27798,7 +27172,6 @@
       <c r="I478" t="n">
         <v>0.95</v>
       </c>
-      <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27855,7 +27228,6 @@
       <c r="I479" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -27912,7 +27284,6 @@
       <c r="I480" t="n">
         <v>1</v>
       </c>
-      <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
           <t>separation</t>
@@ -27969,7 +27340,6 @@
       <c r="I481" t="n">
         <v>0.325</v>
       </c>
-      <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28026,7 +27396,6 @@
       <c r="I482" t="n">
         <v>0.95</v>
       </c>
-      <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28083,7 +27452,6 @@
       <c r="I483" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28140,7 +27508,6 @@
       <c r="I484" t="n">
         <v>1</v>
       </c>
-      <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28197,7 +27564,6 @@
       <c r="I485" t="n">
         <v>0.325</v>
       </c>
-      <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28254,7 +27620,6 @@
       <c r="I486" t="n">
         <v>0.95</v>
       </c>
-      <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28311,7 +27676,6 @@
       <c r="I487" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28368,7 +27732,6 @@
       <c r="I488" t="n">
         <v>1</v>
       </c>
-      <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28425,7 +27788,6 @@
       <c r="I489" t="n">
         <v>0.325</v>
       </c>
-      <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28482,7 +27844,6 @@
       <c r="I490" t="n">
         <v>0.95</v>
       </c>
-      <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28539,7 +27900,6 @@
       <c r="I491" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28596,7 +27956,6 @@
       <c r="I492" t="n">
         <v>1</v>
       </c>
-      <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28653,7 +28012,6 @@
       <c r="I493" t="n">
         <v>0.325</v>
       </c>
-      <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28710,7 +28068,6 @@
       <c r="I494" t="n">
         <v>0.95</v>
       </c>
-      <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28767,7 +28124,6 @@
       <c r="I495" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28824,7 +28180,6 @@
       <c r="I496" t="n">
         <v>1</v>
       </c>
-      <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28881,7 +28236,6 @@
       <c r="I497" t="n">
         <v>0.325</v>
       </c>
-      <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
           <t>separation</t>
@@ -28938,7 +28292,6 @@
       <c r="I498" t="n">
         <v>0.95</v>
       </c>
-      <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -28995,7 +28348,6 @@
       <c r="I499" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29052,7 +28404,6 @@
       <c r="I500" t="n">
         <v>1</v>
       </c>
-      <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29109,7 +28460,6 @@
       <c r="I501" t="n">
         <v>0.325</v>
       </c>
-      <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29166,7 +28516,6 @@
       <c r="I502" t="n">
         <v>0.95</v>
       </c>
-      <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29223,7 +28572,6 @@
       <c r="I503" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29280,7 +28628,6 @@
       <c r="I504" t="n">
         <v>1</v>
       </c>
-      <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29337,7 +28684,6 @@
       <c r="I505" t="n">
         <v>0.325</v>
       </c>
-      <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29394,7 +28740,6 @@
       <c r="I506" t="n">
         <v>0.95</v>
       </c>
-      <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29451,7 +28796,6 @@
       <c r="I507" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29508,7 +28852,6 @@
       <c r="I508" t="n">
         <v>1</v>
       </c>
-      <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29565,7 +28908,6 @@
       <c r="I509" t="n">
         <v>0.325</v>
       </c>
-      <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29622,7 +28964,6 @@
       <c r="I510" t="n">
         <v>0.95</v>
       </c>
-      <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29679,7 +29020,6 @@
       <c r="I511" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29736,7 +29076,6 @@
       <c r="I512" t="n">
         <v>1</v>
       </c>
-      <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29793,7 +29132,6 @@
       <c r="I513" t="n">
         <v>0.325</v>
       </c>
-      <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
           <t>separation</t>
@@ -29850,7 +29188,6 @@
       <c r="I514" t="n">
         <v>0.95</v>
       </c>
-      <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29907,7 +29244,6 @@
       <c r="I515" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -29964,7 +29300,6 @@
       <c r="I516" t="n">
         <v>1</v>
       </c>
-      <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30021,7 +29356,6 @@
       <c r="I517" t="n">
         <v>0.325</v>
       </c>
-      <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30078,7 +29412,6 @@
       <c r="I518" t="n">
         <v>0.95</v>
       </c>
-      <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30135,7 +29468,6 @@
       <c r="I519" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30192,7 +29524,6 @@
       <c r="I520" t="n">
         <v>1</v>
       </c>
-      <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30249,7 +29580,6 @@
       <c r="I521" t="n">
         <v>0.325</v>
       </c>
-      <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30306,7 +29636,6 @@
       <c r="I522" t="n">
         <v>0.95</v>
       </c>
-      <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30363,7 +29692,6 @@
       <c r="I523" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30420,7 +29748,6 @@
       <c r="I524" t="n">
         <v>1</v>
       </c>
-      <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30477,7 +29804,6 @@
       <c r="I525" t="n">
         <v>0.325</v>
       </c>
-      <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30534,7 +29860,6 @@
       <c r="I526" t="n">
         <v>0.95</v>
       </c>
-      <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30591,7 +29916,6 @@
       <c r="I527" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30648,7 +29972,6 @@
       <c r="I528" t="n">
         <v>1</v>
       </c>
-      <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30705,7 +30028,6 @@
       <c r="I529" t="n">
         <v>0.325</v>
       </c>
-      <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30762,7 +30084,6 @@
       <c r="I530" t="n">
         <v>0.95</v>
       </c>
-      <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30819,7 +30140,6 @@
       <c r="I531" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -30876,7 +30196,6 @@
       <c r="I532" t="n">
         <v>1</v>
       </c>
-      <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30933,7 +30252,6 @@
       <c r="I533" t="n">
         <v>0.325</v>
       </c>
-      <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
           <t>separation</t>
@@ -30990,7 +30308,6 @@
       <c r="I534" t="n">
         <v>0.95</v>
       </c>
-      <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31047,7 +30364,6 @@
       <c r="I535" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31104,7 +30420,6 @@
       <c r="I536" t="n">
         <v>1</v>
       </c>
-      <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31161,7 +30476,6 @@
       <c r="I537" t="n">
         <v>0.325</v>
       </c>
-      <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31218,7 +30532,6 @@
       <c r="I538" t="n">
         <v>0.95</v>
       </c>
-      <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31275,7 +30588,6 @@
       <c r="I539" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31332,7 +30644,6 @@
       <c r="I540" t="n">
         <v>1</v>
       </c>
-      <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31389,7 +30700,6 @@
       <c r="I541" t="n">
         <v>0.325</v>
       </c>
-      <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31446,7 +30756,6 @@
       <c r="I542" t="n">
         <v>0.95</v>
       </c>
-      <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31503,7 +30812,6 @@
       <c r="I543" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31560,7 +30868,6 @@
       <c r="I544" t="n">
         <v>1</v>
       </c>
-      <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31617,7 +30924,6 @@
       <c r="I545" t="n">
         <v>0.325</v>
       </c>
-      <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31674,7 +30980,6 @@
       <c r="I546" t="n">
         <v>0.95</v>
       </c>
-      <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31731,7 +31036,6 @@
       <c r="I547" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31788,7 +31092,6 @@
       <c r="I548" t="n">
         <v>1</v>
       </c>
-      <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31845,7 +31148,6 @@
       <c r="I549" t="n">
         <v>0.325</v>
       </c>
-      <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
           <t>separation</t>
@@ -31902,7 +31204,6 @@
       <c r="I550" t="n">
         <v>0.95</v>
       </c>
-      <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -31959,7 +31260,6 @@
       <c r="I551" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32016,7 +31316,6 @@
       <c r="I552" t="n">
         <v>1</v>
       </c>
-      <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32073,7 +31372,6 @@
       <c r="I553" t="n">
         <v>0.325</v>
       </c>
-      <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32130,7 +31428,6 @@
       <c r="I554" t="n">
         <v>0.95</v>
       </c>
-      <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32187,7 +31484,6 @@
       <c r="I555" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32244,7 +31540,6 @@
       <c r="I556" t="n">
         <v>1</v>
       </c>
-      <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32301,7 +31596,6 @@
       <c r="I557" t="n">
         <v>0.325</v>
       </c>
-      <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32358,7 +31652,6 @@
       <c r="I558" t="n">
         <v>0.95</v>
       </c>
-      <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32415,7 +31708,6 @@
       <c r="I559" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32472,7 +31764,6 @@
       <c r="I560" t="n">
         <v>1</v>
       </c>
-      <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32529,7 +31820,6 @@
       <c r="I561" t="n">
         <v>0.325</v>
       </c>
-      <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32586,7 +31876,6 @@
       <c r="I562" t="n">
         <v>0.95</v>
       </c>
-      <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32643,7 +31932,6 @@
       <c r="I563" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32700,7 +31988,6 @@
       <c r="I564" t="n">
         <v>1</v>
       </c>
-      <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32757,7 +32044,6 @@
       <c r="I565" t="n">
         <v>0.325</v>
       </c>
-      <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32814,7 +32100,6 @@
       <c r="I566" t="n">
         <v>0.95</v>
       </c>
-      <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32871,7 +32156,6 @@
       <c r="I567" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -32928,7 +32212,6 @@
       <c r="I568" t="n">
         <v>1</v>
       </c>
-      <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
           <t>separation</t>
@@ -32985,7 +32268,6 @@
       <c r="I569" t="n">
         <v>0.325</v>
       </c>
-      <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33042,7 +32324,6 @@
       <c r="I570" t="n">
         <v>0.95</v>
       </c>
-      <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33099,7 +32380,6 @@
       <c r="I571" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33156,7 +32436,6 @@
       <c r="I572" t="n">
         <v>1</v>
       </c>
-      <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33213,7 +32492,6 @@
       <c r="I573" t="n">
         <v>0.325</v>
       </c>
-      <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33270,7 +32548,6 @@
       <c r="I574" t="n">
         <v>0.95</v>
       </c>
-      <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33327,7 +32604,6 @@
       <c r="I575" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33384,7 +32660,6 @@
       <c r="I576" t="n">
         <v>1</v>
       </c>
-      <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33441,7 +32716,6 @@
       <c r="I577" t="n">
         <v>0.325</v>
       </c>
-      <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33498,7 +32772,6 @@
       <c r="I578" t="n">
         <v>0.95</v>
       </c>
-      <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33555,7 +32828,6 @@
       <c r="I579" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33612,7 +32884,6 @@
       <c r="I580" t="n">
         <v>1</v>
       </c>
-      <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33669,7 +32940,6 @@
       <c r="I581" t="n">
         <v>0.325</v>
       </c>
-      <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33726,7 +32996,6 @@
       <c r="I582" t="n">
         <v>0.95</v>
       </c>
-      <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33783,7 +33052,6 @@
       <c r="I583" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -33840,7 +33108,6 @@
       <c r="I584" t="n">
         <v>1</v>
       </c>
-      <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33897,7 +33164,6 @@
       <c r="I585" t="n">
         <v>0.325</v>
       </c>
-      <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
           <t>separation</t>
@@ -33954,7 +33220,6 @@
       <c r="I586" t="n">
         <v>0.95</v>
       </c>
-      <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34011,7 +33276,6 @@
       <c r="I587" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34068,7 +33332,6 @@
       <c r="I588" t="n">
         <v>1</v>
       </c>
-      <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34125,7 +33388,6 @@
       <c r="I589" t="n">
         <v>0.325</v>
       </c>
-      <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34182,7 +33444,6 @@
       <c r="I590" t="n">
         <v>0.95</v>
       </c>
-      <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34239,7 +33500,6 @@
       <c r="I591" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34296,7 +33556,6 @@
       <c r="I592" t="n">
         <v>1</v>
       </c>
-      <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34353,7 +33612,6 @@
       <c r="I593" t="n">
         <v>0.325</v>
       </c>
-      <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34410,7 +33668,6 @@
       <c r="I594" t="n">
         <v>0.95</v>
       </c>
-      <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34467,7 +33724,6 @@
       <c r="I595" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34524,7 +33780,6 @@
       <c r="I596" t="n">
         <v>1</v>
       </c>
-      <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34581,7 +33836,6 @@
       <c r="I597" t="n">
         <v>0.325</v>
       </c>
-      <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34638,7 +33892,6 @@
       <c r="I598" t="n">
         <v>0.95</v>
       </c>
-      <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34695,7 +33948,6 @@
       <c r="I599" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34752,7 +34004,6 @@
       <c r="I600" t="n">
         <v>1</v>
       </c>
-      <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34809,7 +34060,6 @@
       <c r="I601" t="n">
         <v>0.325</v>
       </c>
-      <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
           <t>separation</t>
@@ -34866,7 +34116,6 @@
       <c r="I602" t="n">
         <v>0.95</v>
       </c>
-      <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34923,7 +34172,6 @@
       <c r="I603" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -34980,7 +34228,6 @@
       <c r="I604" t="n">
         <v>1</v>
       </c>
-      <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35037,7 +34284,6 @@
       <c r="I605" t="n">
         <v>0.325</v>
       </c>
-      <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35094,7 +34340,6 @@
       <c r="I606" t="n">
         <v>0.95</v>
       </c>
-      <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35151,7 +34396,6 @@
       <c r="I607" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35208,7 +34452,6 @@
       <c r="I608" t="n">
         <v>1</v>
       </c>
-      <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35265,7 +34508,6 @@
       <c r="I609" t="n">
         <v>0.325</v>
       </c>
-      <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35322,7 +34564,6 @@
       <c r="I610" t="n">
         <v>0.95</v>
       </c>
-      <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35379,7 +34620,6 @@
       <c r="I611" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35436,7 +34676,6 @@
       <c r="I612" t="n">
         <v>1</v>
       </c>
-      <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35493,7 +34732,6 @@
       <c r="I613" t="n">
         <v>0.325</v>
       </c>
-      <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35550,7 +34788,6 @@
       <c r="I614" t="n">
         <v>0.95</v>
       </c>
-      <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35607,7 +34844,6 @@
       <c r="I615" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35664,7 +34900,6 @@
       <c r="I616" t="n">
         <v>1</v>
       </c>
-      <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35721,7 +34956,6 @@
       <c r="I617" t="n">
         <v>0.325</v>
       </c>
-      <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35778,7 +35012,6 @@
       <c r="I618" t="n">
         <v>0.95</v>
       </c>
-      <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35835,7 +35068,6 @@
       <c r="I619" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -35892,7 +35124,6 @@
       <c r="I620" t="n">
         <v>1</v>
       </c>
-      <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
           <t>separation</t>
@@ -35949,7 +35180,6 @@
       <c r="I621" t="n">
         <v>0.325</v>
       </c>
-      <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36006,7 +35236,6 @@
       <c r="I622" t="n">
         <v>0.95</v>
       </c>
-      <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36063,7 +35292,6 @@
       <c r="I623" t="n">
         <v>0.3625</v>
       </c>
-      <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36120,7 +35348,6 @@
       <c r="I624" t="n">
         <v>1</v>
       </c>
-      <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36177,7 +35404,6 @@
       <c r="I625" t="n">
         <v>0.325</v>
       </c>
-      <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36234,7 +35460,6 @@
       <c r="I626" t="n">
         <v>0.9</v>
       </c>
-      <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36291,7 +35516,6 @@
       <c r="I627" t="n">
         <v>0.4</v>
       </c>
-      <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36348,7 +35572,6 @@
       <c r="I628" t="n">
         <v>0.65</v>
       </c>
-      <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36405,7 +35628,6 @@
       <c r="I629" t="n">
         <v>0.5875</v>
       </c>
-      <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36462,7 +35684,6 @@
       <c r="I630" t="n">
         <v>0.7</v>
       </c>
-      <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36519,7 +35740,6 @@
       <c r="I631" t="n">
         <v>0.55</v>
       </c>
-      <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
           <t>reuse_sorting</t>
@@ -36576,7 +35796,6 @@
       <c r="I632" t="n">
         <v>0.45</v>
       </c>
-      <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
           <t>separation</t>
@@ -36633,7 +35852,6 @@
       <c r="I633" t="n">
         <v>0.7375</v>
       </c>
-      <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
           <t>separation</t>
